--- a/data/raw/fiscal/2021年广东省财力.xlsx
+++ b/data/raw/fiscal/2021年广东省财力.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\远东\4.业务发展\财力数据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chen\Desktop\P1\credit-rating-bd-platform\data\raw\fiscal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAB27371-D23B-48F0-B864-41C72562610B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B816029-2F4B-48D3-8E9F-41FDEB714D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{BD794F0D-76C5-4B2E-85AF-AED130B7B615}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BD794F0D-76C5-4B2E-85AF-AED130B7B615}"/>
   </bookViews>
   <sheets>
     <sheet name="广东" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="114">
   <si>
     <t>序号</t>
   </si>
@@ -51,293 +54,690 @@
     <t>广东省</t>
   </si>
   <si>
-    <t>福州市</t>
-  </si>
-  <si>
-    <t>泉州市</t>
-  </si>
-  <si>
-    <t>厦门市</t>
-  </si>
-  <si>
-    <t>漳州市</t>
-  </si>
-  <si>
-    <t>宁德市</t>
-  </si>
-  <si>
-    <t>龙岩市</t>
-  </si>
-  <si>
-    <t>晋江市</t>
-  </si>
-  <si>
-    <t>三明市</t>
-  </si>
-  <si>
-    <t>莆田市</t>
-  </si>
-  <si>
-    <t>鼓楼区</t>
-  </si>
-  <si>
-    <t>思明区</t>
-  </si>
-  <si>
-    <t>南平市</t>
-  </si>
-  <si>
-    <t>湖里区</t>
-  </si>
-  <si>
-    <t>南安市</t>
-  </si>
-  <si>
-    <t>惠安县</t>
-  </si>
-  <si>
-    <t>福清市</t>
-  </si>
-  <si>
-    <t>龙海区</t>
-  </si>
-  <si>
-    <t>长乐区</t>
-  </si>
-  <si>
-    <t>新罗区</t>
-  </si>
-  <si>
-    <t>蕉城区</t>
-  </si>
-  <si>
-    <t>石狮市</t>
-  </si>
-  <si>
-    <t>晋安区</t>
-  </si>
-  <si>
-    <t>仓山区</t>
-  </si>
-  <si>
-    <t>海沧区</t>
-  </si>
-  <si>
-    <t>闽侯县</t>
-  </si>
-  <si>
-    <t>集美区</t>
-  </si>
-  <si>
-    <t>安溪县</t>
-  </si>
-  <si>
-    <t>芗城区</t>
-  </si>
-  <si>
-    <t>丰泽区</t>
-  </si>
-  <si>
-    <t>翔安区</t>
-  </si>
-  <si>
-    <t>鲤城区</t>
-  </si>
-  <si>
-    <t>福安市</t>
-  </si>
-  <si>
-    <t>三元区</t>
-  </si>
-  <si>
-    <t>连江县</t>
-  </si>
-  <si>
-    <t>台江区</t>
-  </si>
-  <si>
-    <t>泉港区</t>
-  </si>
-  <si>
-    <t>同安区</t>
-  </si>
-  <si>
-    <t>马尾区</t>
-  </si>
-  <si>
-    <t>涵江区</t>
-  </si>
-  <si>
-    <t>荔城区</t>
-  </si>
-  <si>
-    <t>漳浦县</t>
-  </si>
-  <si>
-    <t>仙游县</t>
-  </si>
-  <si>
-    <t>永春县</t>
-  </si>
-  <si>
-    <t>城厢区</t>
-  </si>
-  <si>
-    <t>秀屿区</t>
-  </si>
-  <si>
-    <t>永安市</t>
-  </si>
-  <si>
-    <t>上杭县</t>
-  </si>
-  <si>
-    <t>福鼎市</t>
-  </si>
-  <si>
-    <t>延平区</t>
-  </si>
-  <si>
-    <t>闽清县</t>
-  </si>
-  <si>
-    <t>龙文区</t>
-  </si>
-  <si>
-    <t>长泰区</t>
-  </si>
-  <si>
-    <t>南靖县</t>
-  </si>
-  <si>
-    <t>罗源县</t>
-  </si>
-  <si>
-    <t>沙县区</t>
-  </si>
-  <si>
-    <t>永泰县</t>
-  </si>
-  <si>
-    <t>平潭县</t>
-  </si>
-  <si>
-    <t>洛江区</t>
-  </si>
-  <si>
-    <t>诏安县</t>
-  </si>
-  <si>
-    <t>德化县</t>
-  </si>
-  <si>
-    <t>长汀县</t>
-  </si>
-  <si>
-    <t>永定区</t>
-  </si>
-  <si>
-    <t>霞浦县</t>
-  </si>
-  <si>
-    <t>建瓯市</t>
-  </si>
-  <si>
-    <t>漳平市</t>
-  </si>
-  <si>
-    <t>连城县</t>
-  </si>
-  <si>
-    <t>武平县</t>
-  </si>
-  <si>
-    <t>平和县</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>建阳区</t>
-  </si>
-  <si>
-    <t>邵武市</t>
-  </si>
-  <si>
-    <t>大田县</t>
-  </si>
-  <si>
-    <t>尤溪县</t>
-  </si>
-  <si>
-    <t>云霄县</t>
-  </si>
-  <si>
-    <t>宁化县</t>
-  </si>
-  <si>
-    <t>武夷山市</t>
-  </si>
-  <si>
-    <t>古田县</t>
-  </si>
-  <si>
-    <t>东山县</t>
-  </si>
-  <si>
-    <t>华安县</t>
-  </si>
-  <si>
-    <t>浦城县</t>
-  </si>
-  <si>
-    <t>将乐县</t>
-  </si>
-  <si>
-    <t>清流县</t>
-  </si>
-  <si>
-    <t>建宁县</t>
-  </si>
-  <si>
-    <t>顺昌县</t>
-  </si>
-  <si>
-    <t>明溪县</t>
-  </si>
-  <si>
-    <t>光泽县</t>
-  </si>
-  <si>
-    <t>寿宁县</t>
-  </si>
-  <si>
-    <t>屏南县</t>
-  </si>
-  <si>
-    <t>政和县</t>
-  </si>
-  <si>
-    <t>泰宁县</t>
-  </si>
-  <si>
-    <t>周宁县</t>
-  </si>
-  <si>
-    <t>松溪县</t>
-  </si>
-  <si>
-    <t>柘荣县</t>
-  </si>
-  <si>
-    <t>金门县</t>
+    <t>地区名称</t>
+  </si>
+  <si>
+    <t>惠阳区</t>
+  </si>
+  <si>
+    <t>白云区</t>
+  </si>
+  <si>
+    <t>三水区</t>
+  </si>
+  <si>
+    <t>光明区</t>
+  </si>
+  <si>
+    <t>天河区</t>
+  </si>
+  <si>
+    <t>花都区</t>
+  </si>
+  <si>
+    <t>番禺区</t>
+  </si>
+  <si>
+    <t>罗湖区</t>
+  </si>
+  <si>
+    <t>梅州市</t>
+  </si>
+  <si>
+    <t>南沙区</t>
+  </si>
+  <si>
+    <t>禅城区</t>
+  </si>
+  <si>
+    <t>增城区</t>
+  </si>
+  <si>
+    <t>韶关市</t>
+  </si>
+  <si>
+    <t>肇庆市</t>
+  </si>
+  <si>
+    <t>汕头市</t>
+  </si>
+  <si>
+    <t>黄埔区</t>
+  </si>
+  <si>
+    <t>湛江市</t>
+  </si>
+  <si>
+    <t>龙华区</t>
+  </si>
+  <si>
+    <t>茂名市</t>
+  </si>
+  <si>
+    <t>顺德区</t>
+  </si>
+  <si>
+    <t>南海区</t>
+  </si>
+  <si>
+    <t>福田区</t>
+  </si>
+  <si>
+    <t>珠海市</t>
+  </si>
+  <si>
+    <t>南山区</t>
+  </si>
+  <si>
+    <t>宝安区</t>
+  </si>
+  <si>
+    <t>龙岗区</t>
+  </si>
+  <si>
+    <t>江门市</t>
+  </si>
+  <si>
+    <t>佛山市</t>
+  </si>
+  <si>
+    <t>惠州市</t>
+  </si>
+  <si>
+    <t>深圳市</t>
+  </si>
+  <si>
+    <t>广州市</t>
+  </si>
+  <si>
+    <r>
+      <t>GDP(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亿元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>频度：年度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年份：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2021</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GDP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增速</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">(%) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>频度：年度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年份：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2021</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>一般公共预算收入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亿元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>频度：年度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年份：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2021</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>一般公共预算收入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>税收收入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亿元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>频度：年度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年份：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2021</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>一般公共预算支出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亿元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>频度：年度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年份：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2021</t>
+    </r>
+  </si>
+  <si>
+    <t>坪山区</t>
+  </si>
+  <si>
+    <t>新会区</t>
+  </si>
+  <si>
+    <t>博罗县</t>
+  </si>
+  <si>
+    <t>海珠区</t>
+  </si>
+  <si>
+    <t>越秀区</t>
+  </si>
+  <si>
+    <t>荔湾区</t>
+  </si>
+  <si>
+    <t>金湾区</t>
+  </si>
+  <si>
+    <t>高明区</t>
+  </si>
+  <si>
+    <t>惠城区</t>
+  </si>
+  <si>
+    <t>香洲区</t>
+  </si>
+  <si>
+    <t>鹤山市</t>
+  </si>
+  <si>
+    <t>盐田区</t>
+  </si>
+  <si>
+    <t>台山市</t>
+  </si>
+  <si>
+    <t>斗门区</t>
+  </si>
+  <si>
+    <t>从化区</t>
+  </si>
+  <si>
+    <t>开平市</t>
+  </si>
+  <si>
+    <t>惠东县</t>
+  </si>
+  <si>
+    <t>蓬江区</t>
+  </si>
+  <si>
+    <t>电白区</t>
+  </si>
+  <si>
+    <t>高要区</t>
+  </si>
+  <si>
+    <t>四会市</t>
+  </si>
+  <si>
+    <t>龙门县</t>
+  </si>
+  <si>
+    <t>龙湖区</t>
+  </si>
+  <si>
+    <t>潮阳区</t>
+  </si>
+  <si>
+    <t>廉江市</t>
+  </si>
+  <si>
+    <t>高州市</t>
+  </si>
+  <si>
+    <t>澄海区</t>
+  </si>
+  <si>
+    <t>梅县区</t>
+  </si>
+  <si>
+    <t>江海区</t>
+  </si>
+  <si>
+    <t>吴川市</t>
+  </si>
+  <si>
+    <t>徐闻县</t>
+  </si>
+  <si>
+    <t>恩平市</t>
+  </si>
+  <si>
+    <t>化州市</t>
+  </si>
+  <si>
+    <t>五华县</t>
+  </si>
+  <si>
+    <t>端州区</t>
+  </si>
+  <si>
+    <t>封开县</t>
+  </si>
+  <si>
+    <t>信宜市</t>
+  </si>
+  <si>
+    <t>兴宁市</t>
+  </si>
+  <si>
+    <t>茂南区</t>
+  </si>
+  <si>
+    <t>潮南区</t>
+  </si>
+  <si>
+    <t>金平区</t>
+  </si>
+  <si>
+    <t>雷州市</t>
+  </si>
+  <si>
+    <t>鼎湖区</t>
+  </si>
+  <si>
+    <t>遂溪县</t>
+  </si>
+  <si>
+    <t>德庆县</t>
+  </si>
+  <si>
+    <t>乐昌市</t>
+  </si>
+  <si>
+    <t>翁源县</t>
+  </si>
+  <si>
+    <t>丰顺县</t>
+  </si>
+  <si>
+    <t>梅江区</t>
+  </si>
+  <si>
+    <t>怀集县</t>
+  </si>
+  <si>
+    <t>曲江区</t>
+  </si>
+  <si>
+    <t>霞山区</t>
+  </si>
+  <si>
+    <t>广宁县</t>
+  </si>
+  <si>
+    <t>蕉岭县</t>
+  </si>
+  <si>
+    <t>南雄市</t>
+  </si>
+  <si>
+    <t>麻章区</t>
+  </si>
+  <si>
+    <t>大埔县</t>
+  </si>
+  <si>
+    <t>濠江区</t>
+  </si>
+  <si>
+    <t>武江区</t>
+  </si>
+  <si>
+    <t>乳源瑶族自治县</t>
+  </si>
+  <si>
+    <t>平远县</t>
+  </si>
+  <si>
+    <t>始兴县</t>
+  </si>
+  <si>
+    <t>浈江区</t>
+  </si>
+  <si>
+    <t>新丰县</t>
+  </si>
+  <si>
+    <t>仁化县</t>
+  </si>
+  <si>
+    <t>坡头区</t>
+  </si>
+  <si>
+    <t>赤坎区</t>
+  </si>
+  <si>
+    <t>南澳县</t>
+  </si>
+  <si>
+    <t>广东省</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,6 +749,13 @@
       <sz val="9"/>
       <name val="Times New Roman"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -374,11 +781,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -695,13 +1105,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C6BD17C-DDE6-444A-9734-EECF8FCC8C3A}">
-  <dimension ref="A1:G95"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:G241"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="15.5" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -724,12 +1134,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="C2" s="1">
         <v>124369.67</v>
@@ -747,2147 +1157,7183 @@
         <v>18247.009999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C3" s="1">
-        <v>11324.48</v>
+        <v>31473.84</v>
       </c>
       <c r="D3">
-        <v>8.4</v>
-      </c>
-      <c r="E3">
-        <v>749.85</v>
-      </c>
-      <c r="F3">
-        <v>563.77</v>
-      </c>
-      <c r="G3">
-        <v>925.26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+        <v>7.26</v>
+      </c>
+      <c r="E3" s="1">
+        <v>4257.7</v>
+      </c>
+      <c r="F3" s="1">
+        <v>3450.41</v>
+      </c>
+      <c r="G3" s="1">
+        <v>4570.22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1">
-        <v>11304.17</v>
+        <v>28848.959999999999</v>
       </c>
       <c r="D4">
-        <v>8.1</v>
-      </c>
-      <c r="E4">
-        <v>504.54</v>
-      </c>
-      <c r="F4">
-        <v>394.32</v>
-      </c>
-      <c r="G4">
-        <v>672.28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+        <v>8.32</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1884.26</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1410.06</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3021.18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1">
-        <v>7033.89</v>
+        <v>12349.22</v>
       </c>
       <c r="D5">
-        <v>8.1</v>
+        <v>8.61</v>
       </c>
       <c r="E5">
-        <v>880.96</v>
+        <v>808.26</v>
       </c>
       <c r="F5">
-        <v>676.27</v>
+        <v>545.71</v>
       </c>
       <c r="G5" s="1">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1072.01</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1">
-        <v>5025.3999999999996</v>
+        <v>5259.64</v>
       </c>
       <c r="D6">
-        <v>7.7</v>
+        <v>10.83</v>
       </c>
       <c r="E6">
-        <v>246.18</v>
+        <v>455.39</v>
       </c>
       <c r="F6">
-        <v>176.19</v>
+        <v>335.02</v>
       </c>
       <c r="G6">
-        <v>420.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+        <v>663.31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1">
-        <v>3151.08</v>
+        <v>3997.86</v>
       </c>
       <c r="D7">
-        <v>13.3</v>
+        <v>7.52</v>
       </c>
       <c r="E7">
-        <v>158.05000000000001</v>
+        <v>448.19</v>
       </c>
       <c r="F7">
-        <v>117.08</v>
+        <v>314.14</v>
       </c>
       <c r="G7">
-        <v>343.68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+        <v>786.66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1">
-        <v>3081.78</v>
+        <v>7708.74</v>
       </c>
       <c r="D8">
-        <v>7.7</v>
+        <v>9.56</v>
       </c>
       <c r="E8">
-        <v>169.46</v>
+        <v>361.02</v>
       </c>
       <c r="F8">
-        <v>122.73</v>
+        <v>351.5</v>
       </c>
       <c r="G8">
-        <v>344.56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+        <v>402.42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1">
-        <v>2986.41</v>
+        <v>4419.0600000000004</v>
       </c>
       <c r="D9">
-        <v>10.5</v>
+        <v>11.25</v>
       </c>
       <c r="E9">
-        <v>146.19999999999999</v>
+        <v>296</v>
       </c>
       <c r="F9">
-        <v>118.2</v>
+        <v>290.69</v>
       </c>
       <c r="G9">
-        <v>124.77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+        <v>452.16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1">
-        <v>2953.47</v>
+        <v>4968.6099999999997</v>
       </c>
       <c r="D10">
-        <v>5.8</v>
+        <v>-5.36</v>
       </c>
       <c r="E10">
-        <v>113.51</v>
+        <v>292.22000000000003</v>
       </c>
       <c r="F10">
-        <v>80.78</v>
+        <v>259.83</v>
       </c>
       <c r="G10">
-        <v>309.56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+        <v>380.71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1">
-        <v>2882.96</v>
+        <v>3695.31</v>
       </c>
       <c r="D11">
-        <v>6.4</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="E11">
-        <v>153.78</v>
+        <v>279.87</v>
       </c>
       <c r="F11">
-        <v>113.05</v>
+        <v>176.89</v>
       </c>
       <c r="G11">
-        <v>248.08</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+        <v>460.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1">
-        <v>2362.19</v>
+        <v>4128.09</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="E12">
-        <v>35.01</v>
+        <v>274.01</v>
       </c>
       <c r="F12">
-        <v>31.28</v>
+        <v>196.91</v>
       </c>
       <c r="G12">
-        <v>30.09</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+        <v>265.77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1">
-        <v>2258.08</v>
+        <v>3565.66</v>
       </c>
       <c r="D13">
-        <v>8.1999999999999993</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="E13">
-        <v>73.23</v>
+        <v>266.57</v>
       </c>
       <c r="F13">
-        <v>65.72</v>
+        <v>183.16</v>
       </c>
       <c r="G13">
-        <v>109.3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+        <v>289.42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C14" s="1">
-        <v>2117.58</v>
+        <v>5319.86</v>
       </c>
       <c r="D14">
-        <v>6.5</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="E14">
-        <v>102.3</v>
+        <v>214.29</v>
       </c>
       <c r="F14">
-        <v>66.2</v>
+        <v>204.25</v>
       </c>
       <c r="G14">
-        <v>308.51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+        <v>296.29000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C15" s="1">
-        <v>1539.41</v>
+        <v>4187.8900000000003</v>
       </c>
       <c r="D15">
-        <v>7.2</v>
+        <v>8.17</v>
       </c>
       <c r="E15">
-        <v>55.56</v>
+        <v>206.82</v>
       </c>
       <c r="F15">
-        <v>45.03</v>
+        <v>166.91</v>
       </c>
       <c r="G15">
-        <v>81.28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+        <v>357.92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C16" s="1">
-        <v>1536.36</v>
+        <v>3615.7</v>
       </c>
       <c r="D16">
-        <v>9.8000000000000007</v>
+        <v>8.77</v>
       </c>
       <c r="E16">
-        <v>58.62</v>
+        <v>160.4</v>
       </c>
       <c r="F16">
-        <v>50.81</v>
+        <v>97.89</v>
       </c>
       <c r="G16">
-        <v>92.78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+        <v>547.39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C17" s="1">
-        <v>1491.13</v>
+        <v>2807.32</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>9.84</v>
       </c>
       <c r="E17">
-        <v>40.86</v>
+        <v>152.21</v>
       </c>
       <c r="F17">
-        <v>36.1</v>
+        <v>141.16999999999999</v>
       </c>
       <c r="G17">
-        <v>58.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+        <v>292.31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C18" s="1">
-        <v>1414.04</v>
+        <v>3761.42</v>
       </c>
       <c r="D18">
-        <v>10.6</v>
+        <v>7.67</v>
       </c>
       <c r="E18">
-        <v>104.79</v>
+        <v>148.41</v>
       </c>
       <c r="F18">
-        <v>76.239999999999995</v>
+        <v>83</v>
       </c>
       <c r="G18">
-        <v>125.23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+        <v>489.54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C19" s="1">
-        <v>1265.78</v>
+        <v>2719.29</v>
       </c>
       <c r="D19">
-        <v>8.8000000000000007</v>
+        <v>10.81</v>
       </c>
       <c r="E19">
-        <v>18.11</v>
+        <v>146.46</v>
       </c>
       <c r="F19">
-        <v>14.02</v>
+        <v>90.33</v>
       </c>
       <c r="G19">
-        <v>29.89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+        <v>396.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C20" s="1">
-        <v>1143.9000000000001</v>
+        <v>2982.2</v>
       </c>
       <c r="D20">
-        <v>9.4</v>
+        <v>6.54</v>
       </c>
       <c r="E20">
-        <v>62.38</v>
+        <v>146.35</v>
       </c>
       <c r="F20">
-        <v>49.78</v>
+        <v>103.51</v>
       </c>
       <c r="G20">
-        <v>83.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+        <v>412.92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C21" s="1">
-        <v>1109.03</v>
+        <v>2185.35</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="E21">
-        <v>25.85</v>
+        <v>119.74</v>
       </c>
       <c r="F21">
-        <v>20.05</v>
+        <v>85.96</v>
       </c>
       <c r="G21">
-        <v>53.43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+        <v>136.58000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C22" s="1">
-        <v>1098.5899999999999</v>
+        <v>1255.3599999999999</v>
       </c>
       <c r="D22">
-        <v>29.8</v>
+        <v>10.66</v>
       </c>
       <c r="E22">
-        <v>24.84</v>
+        <v>113.85</v>
       </c>
       <c r="F22">
-        <v>23</v>
+        <v>96.86</v>
       </c>
       <c r="G22">
-        <v>41.7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+        <v>156.52000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C23" s="1">
-        <v>1072.51</v>
+        <v>1560.26</v>
       </c>
       <c r="D23">
-        <v>10.4</v>
+        <v>8.67</v>
       </c>
       <c r="E23">
-        <v>40.14</v>
+        <v>109.08</v>
       </c>
       <c r="F23">
-        <v>26.97</v>
+        <v>59.34</v>
       </c>
       <c r="G23">
-        <v>49.35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+        <v>370.19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C24" s="1">
-        <v>1063.28</v>
+        <v>2153.65</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>9.64</v>
       </c>
       <c r="E24">
-        <v>26.61</v>
+        <v>108.2</v>
       </c>
       <c r="F24">
-        <v>19.25</v>
+        <v>86.91</v>
       </c>
       <c r="G24">
-        <v>34.82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+        <v>242.37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C25" s="1">
-        <v>1030.1099999999999</v>
+        <v>2657.7</v>
       </c>
       <c r="D25">
-        <v>9.5</v>
+        <v>9.02</v>
       </c>
       <c r="E25">
-        <v>27.39</v>
+        <v>107.67</v>
       </c>
       <c r="F25">
-        <v>23.46</v>
+        <v>81.290000000000006</v>
       </c>
       <c r="G25">
-        <v>35.06</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+        <v>195.38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26">
-        <v>938.24</v>
+        <v>16</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2508.23</v>
       </c>
       <c r="D26">
-        <v>11.9</v>
+        <v>6.14</v>
       </c>
       <c r="E26">
-        <v>40.14</v>
+        <v>107.29</v>
       </c>
       <c r="F26">
-        <v>29.71</v>
+        <v>102.21</v>
       </c>
       <c r="G26">
-        <v>70.86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+        <v>183.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27">
-        <v>881.16</v>
+        <v>17</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1362.04</v>
       </c>
       <c r="D27">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="E27">
-        <v>95.18</v>
+        <v>95.01</v>
       </c>
       <c r="F27">
-        <v>57.56</v>
+        <v>57.8</v>
       </c>
       <c r="G27">
-        <v>98.71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+        <v>443.07</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28">
-        <v>876</v>
+        <v>14</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1802.98</v>
       </c>
       <c r="D28">
-        <v>6.8</v>
+        <v>6.57</v>
       </c>
       <c r="E28">
-        <v>47.53</v>
+        <v>86.27</v>
       </c>
       <c r="F28">
-        <v>27.32</v>
+        <v>60.51</v>
       </c>
       <c r="G28">
-        <v>84.65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+        <v>170.96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29">
-        <v>845.61</v>
+        <v>12</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1348.43</v>
       </c>
       <c r="D29">
-        <v>10.5</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="E29">
-        <v>32.94</v>
+        <v>78.819999999999993</v>
       </c>
       <c r="F29">
-        <v>24.43</v>
+        <v>75.06</v>
       </c>
       <c r="G29">
-        <v>65.790000000000006</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+        <v>182.37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30">
-        <v>827.34</v>
+        <v>13</v>
+      </c>
+      <c r="C30" s="1">
+        <v>6004.16</v>
       </c>
       <c r="D30">
-        <v>7.8</v>
+        <v>8.16</v>
       </c>
       <c r="E30">
-        <v>18.87</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="F30">
-        <v>14.27</v>
+        <v>61.3</v>
       </c>
       <c r="G30">
-        <v>22.69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+        <v>160.56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31">
-        <v>807.48</v>
+        <v>11</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1407.2</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="E31">
-        <v>17.87</v>
+        <v>71.52</v>
       </c>
       <c r="F31">
-        <v>13.63</v>
+        <v>49.64</v>
       </c>
       <c r="G31">
-        <v>22.47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+        <v>81.67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32">
-        <v>781.79</v>
+        <v>10</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2532.84</v>
       </c>
       <c r="D32">
-        <v>7.3</v>
+        <v>7.95</v>
       </c>
       <c r="E32">
-        <v>26.61</v>
+        <v>69.42</v>
       </c>
       <c r="F32">
-        <v>15.57</v>
+        <v>47.78</v>
       </c>
       <c r="G32">
-        <v>59.08</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+        <v>192.35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33">
-        <v>705.01</v>
+        <v>9</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1588.24</v>
       </c>
       <c r="D33">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
       <c r="E33">
-        <v>13.55</v>
+        <v>64.28</v>
       </c>
       <c r="F33">
-        <v>9.2200000000000006</v>
+        <v>56.08</v>
       </c>
       <c r="G33">
-        <v>20.34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+        <v>83.59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C34">
-        <v>680.41</v>
+        <v>910.09</v>
       </c>
       <c r="D34">
-        <v>6.2</v>
+        <v>11.69</v>
       </c>
       <c r="E34">
-        <v>36.299999999999997</v>
+        <v>64.03</v>
       </c>
       <c r="F34">
-        <v>28.83</v>
+        <v>61.97</v>
       </c>
       <c r="G34">
-        <v>48.39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+        <v>157.85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C35">
-        <v>674.39</v>
+        <v>898.48</v>
       </c>
       <c r="D35">
-        <v>7.1</v>
+        <v>8.86</v>
       </c>
       <c r="E35">
-        <v>11.8</v>
+        <v>58.56</v>
       </c>
       <c r="F35">
-        <v>8.49</v>
+        <v>35.24</v>
       </c>
       <c r="G35">
-        <v>21.57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+        <v>97.73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C36">
-        <v>671.44</v>
+        <v>745.58</v>
       </c>
       <c r="D36">
-        <v>7.2</v>
+        <v>12.8</v>
       </c>
       <c r="E36">
-        <v>36.58</v>
+        <v>56.12</v>
       </c>
       <c r="F36">
-        <v>28.13</v>
+        <v>40.76</v>
       </c>
       <c r="G36">
-        <v>76.739999999999995</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+        <v>104.48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
-      </c>
-      <c r="C37">
-        <v>659.25</v>
+        <v>48</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2405.1999999999998</v>
       </c>
       <c r="D37">
-        <v>8.6</v>
+        <v>9.33</v>
       </c>
       <c r="E37">
-        <v>17.62</v>
+        <v>55.78</v>
       </c>
       <c r="F37">
-        <v>14.55</v>
+        <v>36.96</v>
       </c>
       <c r="G37">
-        <v>22.23</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+        <v>132.38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38">
-        <v>657.8</v>
+        <v>49</v>
+      </c>
+      <c r="C38" s="1">
+        <v>3606.39</v>
       </c>
       <c r="D38">
-        <v>-9.9</v>
+        <v>6.01</v>
       </c>
       <c r="E38">
-        <v>28.06</v>
+        <v>54.05</v>
       </c>
       <c r="F38">
-        <v>23.62</v>
+        <v>39.79</v>
       </c>
       <c r="G38">
-        <v>27.06</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+        <v>132.03</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39">
-        <v>640.36</v>
+        <v>50</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1203.1099999999999</v>
       </c>
       <c r="D39">
-        <v>6.8</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="E39">
-        <v>30.66</v>
+        <v>53.14</v>
       </c>
       <c r="F39">
-        <v>19.87</v>
+        <v>36.29</v>
       </c>
       <c r="G39">
-        <v>83.23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+        <v>105.22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C40">
-        <v>639.84</v>
+        <v>814.85</v>
       </c>
       <c r="D40">
-        <v>3.5</v>
+        <v>11.32</v>
       </c>
       <c r="E40">
-        <v>22.95</v>
+        <v>48.14</v>
       </c>
       <c r="F40">
-        <v>15.92</v>
+        <v>38.89</v>
       </c>
       <c r="G40">
-        <v>28.04</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C41">
-        <v>639.41999999999996</v>
+        <v>983.01</v>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>7.27</v>
       </c>
       <c r="E41">
-        <v>23.61</v>
+        <v>45.81</v>
       </c>
       <c r="F41">
-        <v>20.99</v>
+        <v>29.33</v>
       </c>
       <c r="G41">
-        <v>27.03</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+        <v>60.63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
-      </c>
-      <c r="C42">
-        <v>618.80999999999995</v>
+        <v>53</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1809.06</v>
       </c>
       <c r="D42">
-        <v>8.1999999999999993</v>
+        <v>11.8</v>
       </c>
       <c r="E42">
-        <v>30.62</v>
+        <v>44.08</v>
       </c>
       <c r="F42">
-        <v>25.05</v>
+        <v>35.5</v>
       </c>
       <c r="G42">
-        <v>36.729999999999997</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+        <v>81.03</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>48</v>
-      </c>
-      <c r="C43">
-        <v>583.61</v>
+        <v>54</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2612.85</v>
       </c>
       <c r="D43">
-        <v>9.8000000000000007</v>
+        <v>6.64</v>
       </c>
       <c r="E43">
-        <v>36.630000000000003</v>
+        <v>41.41</v>
       </c>
       <c r="F43">
-        <v>17.440000000000001</v>
+        <v>32.020000000000003</v>
       </c>
       <c r="G43">
-        <v>56.25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C44">
-        <v>558.34</v>
+        <v>436.82</v>
       </c>
       <c r="D44">
-        <v>6</v>
+        <v>9.68</v>
       </c>
       <c r="E44">
-        <v>26.72</v>
+        <v>36.51</v>
       </c>
       <c r="F44">
-        <v>19.829999999999998</v>
+        <v>23.37</v>
       </c>
       <c r="G44">
-        <v>54.84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+        <v>49.51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C45">
-        <v>541.23</v>
+        <v>759.28</v>
       </c>
       <c r="D45">
-        <v>6.1</v>
+        <v>10.86</v>
       </c>
       <c r="E45">
-        <v>13.19</v>
+        <v>36.44</v>
       </c>
       <c r="F45">
-        <v>9.18</v>
+        <v>34.5</v>
       </c>
       <c r="G45">
-        <v>37.950000000000003</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+        <v>67.83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C46">
-        <v>538.76</v>
+        <v>500.38</v>
       </c>
       <c r="D46">
-        <v>7.7</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="E46">
-        <v>25.13</v>
+        <v>35.67</v>
       </c>
       <c r="F46">
-        <v>20.29</v>
+        <v>22.21</v>
       </c>
       <c r="G46">
-        <v>31.74</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+        <v>77.19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C47">
-        <v>527.63</v>
+        <v>468.34</v>
       </c>
       <c r="D47">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="E47">
-        <v>15.01</v>
+        <v>35.39</v>
       </c>
       <c r="F47">
-        <v>12.43</v>
+        <v>25.82</v>
       </c>
       <c r="G47">
-        <v>23.34</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+        <v>69.72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C48">
-        <v>487.99</v>
+        <v>415.92</v>
       </c>
       <c r="D48">
-        <v>6.3</v>
+        <v>3.62</v>
       </c>
       <c r="E48">
-        <v>20.02</v>
+        <v>31.77</v>
       </c>
       <c r="F48">
-        <v>15.74</v>
+        <v>22.06</v>
       </c>
       <c r="G48">
-        <v>29.16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+        <v>91.48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C49">
-        <v>466.36</v>
+        <v>435.9</v>
       </c>
       <c r="D49">
-        <v>9.4</v>
+        <v>8.26</v>
       </c>
       <c r="E49">
-        <v>30.34</v>
+        <v>31.65</v>
       </c>
       <c r="F49">
-        <v>19.05</v>
+        <v>19.04</v>
       </c>
       <c r="G49">
-        <v>58.1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+        <v>51.94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C50">
-        <v>454.24</v>
+        <v>700.98</v>
       </c>
       <c r="D50">
-        <v>0.5</v>
+        <v>10.75</v>
       </c>
       <c r="E50">
-        <v>23.41</v>
+        <v>31.47</v>
       </c>
       <c r="F50">
-        <v>15.01</v>
+        <v>19.5</v>
       </c>
       <c r="G50">
-        <v>40.83</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+        <v>87.74</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C51">
-        <v>438.69</v>
+        <v>828.79</v>
       </c>
       <c r="D51">
-        <v>4.4000000000000004</v>
+        <v>9.06</v>
       </c>
       <c r="E51">
-        <v>7.36</v>
+        <v>31.4</v>
       </c>
       <c r="F51">
-        <v>5.05</v>
+        <v>19.350000000000001</v>
       </c>
       <c r="G51">
-        <v>23.57</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+        <v>42.65</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C52">
-        <v>389.78</v>
+        <v>765.51</v>
       </c>
       <c r="D52">
-        <v>6.2</v>
+        <v>8.92</v>
       </c>
       <c r="E52">
-        <v>18.46</v>
+        <v>22.65</v>
       </c>
       <c r="F52">
-        <v>16.489999999999998</v>
+        <v>15.71</v>
       </c>
       <c r="G52">
-        <v>35.29</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+        <v>83.87</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C53">
-        <v>375.89</v>
+        <v>513.21</v>
       </c>
       <c r="D53">
-        <v>9.1</v>
+        <v>13.54</v>
       </c>
       <c r="E53">
-        <v>13.89</v>
+        <v>22.44</v>
       </c>
       <c r="F53">
-        <v>13.06</v>
+        <v>12.88</v>
       </c>
       <c r="G53">
-        <v>15.56</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+        <v>52.07</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C54">
-        <v>375.23</v>
+        <v>722.5</v>
       </c>
       <c r="D54">
-        <v>7.5</v>
+        <v>12.63</v>
       </c>
       <c r="E54">
-        <v>13.49</v>
+        <v>20.440000000000001</v>
       </c>
       <c r="F54">
-        <v>12.12</v>
+        <v>14.71</v>
       </c>
       <c r="G54">
-        <v>24.62</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+        <v>36.119999999999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C55">
-        <v>365.9</v>
+        <v>189.19</v>
       </c>
       <c r="D55">
-        <v>5.3</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="E55">
-        <v>9.81</v>
+        <v>19.45</v>
       </c>
       <c r="F55">
-        <v>6.71</v>
+        <v>6.82</v>
       </c>
       <c r="G55">
-        <v>23.29</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+        <v>43.32</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C56">
-        <v>359.06</v>
+        <v>605.58000000000004</v>
       </c>
       <c r="D56">
-        <v>7.3</v>
+        <v>6.72</v>
       </c>
       <c r="E56">
-        <v>11.85</v>
+        <v>18.920000000000002</v>
       </c>
       <c r="F56">
-        <v>9.74</v>
+        <v>14.93</v>
       </c>
       <c r="G56">
-        <v>25.3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+        <v>37.22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C57">
-        <v>354.44</v>
+        <v>533.02</v>
       </c>
       <c r="D57">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="E57">
-        <v>10.48</v>
+        <v>18.440000000000001</v>
       </c>
       <c r="F57">
-        <v>8.8000000000000007</v>
+        <v>13.54</v>
       </c>
       <c r="G57">
-        <v>27.36</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+        <v>74.98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C58">
-        <v>339.31</v>
+        <v>513.17999999999995</v>
       </c>
       <c r="D58">
-        <v>5.9</v>
+        <v>7.02</v>
       </c>
       <c r="E58">
-        <v>13.18</v>
+        <v>17.53</v>
       </c>
       <c r="F58">
-        <v>9.3699999999999992</v>
+        <v>7.71</v>
       </c>
       <c r="G58">
-        <v>33.9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+        <v>83.05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C59">
-        <v>339.2</v>
+        <v>685.43</v>
       </c>
       <c r="D59">
-        <v>5.8</v>
+        <v>7.55</v>
       </c>
       <c r="E59">
-        <v>54.93</v>
+        <v>17.18</v>
       </c>
       <c r="F59">
-        <v>43.94</v>
+        <v>8.82</v>
       </c>
       <c r="G59">
-        <v>85.31</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+        <v>90.05</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C60">
-        <v>333.13</v>
+        <v>489.66</v>
       </c>
       <c r="D60">
-        <v>13.9</v>
+        <v>6.05</v>
       </c>
       <c r="E60">
-        <v>15.4</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="F60">
-        <v>12.89</v>
+        <v>12.22</v>
       </c>
       <c r="G60">
-        <v>16.63</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+        <v>41.83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C61">
-        <v>328.27</v>
+        <v>237.83</v>
       </c>
       <c r="D61">
-        <v>8.5</v>
+        <v>6.25</v>
       </c>
       <c r="E61">
-        <v>7.76</v>
+        <v>16.38</v>
       </c>
       <c r="F61">
-        <v>5.08</v>
+        <v>10.08</v>
       </c>
       <c r="G61">
-        <v>28.97</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C62">
-        <v>327.48</v>
+        <v>289.77</v>
       </c>
       <c r="D62">
-        <v>11.6</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="E62">
-        <v>14.63</v>
+        <v>15.75</v>
       </c>
       <c r="F62">
-        <v>11.07</v>
+        <v>12.85</v>
       </c>
       <c r="G62">
-        <v>33.18</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C63">
-        <v>318.14999999999998</v>
+        <v>302.02</v>
       </c>
       <c r="D63">
-        <v>7</v>
+        <v>7.17</v>
       </c>
       <c r="E63">
-        <v>10.15</v>
+        <v>15.01</v>
       </c>
       <c r="F63">
-        <v>7.43</v>
+        <v>7.38</v>
       </c>
       <c r="G63">
-        <v>39.840000000000003</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C64">
-        <v>312.10000000000002</v>
+        <v>217.6</v>
       </c>
       <c r="D64">
-        <v>8.1999999999999993</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="E64">
-        <v>11</v>
+        <v>14.04</v>
       </c>
       <c r="F64">
-        <v>7.66</v>
+        <v>4.03</v>
       </c>
       <c r="G64">
-        <v>28.03</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+        <v>48.64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C65">
-        <v>310.22000000000003</v>
+        <v>207.91</v>
       </c>
       <c r="D65">
-        <v>12.8</v>
+        <v>7.08</v>
       </c>
       <c r="E65">
-        <v>13.41</v>
+        <v>13.89</v>
       </c>
       <c r="F65">
-        <v>8.08</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="G65">
-        <v>42.19</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C66">
-        <v>295.62</v>
+        <v>624.91</v>
       </c>
       <c r="D66">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="E66">
-        <v>11.2</v>
+        <v>13.7</v>
       </c>
       <c r="F66">
-        <v>5.76</v>
+        <v>7.34</v>
       </c>
       <c r="G66">
-        <v>32.14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
+        <v>82.79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C67">
-        <v>295.02999999999997</v>
+        <v>176.08</v>
       </c>
       <c r="D67">
-        <v>8.5</v>
+        <v>5.15</v>
       </c>
       <c r="E67">
-        <v>10.34</v>
+        <v>12.16</v>
       </c>
       <c r="F67">
-        <v>8.39</v>
+        <v>7.33</v>
       </c>
       <c r="G67">
-        <v>25.71</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
+        <v>84.09</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C68">
-        <v>294.35000000000002</v>
+        <v>473.49</v>
       </c>
       <c r="D68">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="E68">
-        <v>7.91</v>
+        <v>11.97</v>
       </c>
       <c r="F68">
-        <v>4.57</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="G68">
-        <v>26.95</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.4">
+        <v>28.84</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C69">
-        <v>286.76</v>
+        <v>163.87</v>
       </c>
       <c r="D69">
-        <v>6.4</v>
+        <v>9.98</v>
       </c>
       <c r="E69">
-        <v>10.5</v>
+        <v>11.86</v>
       </c>
       <c r="F69">
-        <v>6.67</v>
+        <v>4.43</v>
       </c>
       <c r="G69">
-        <v>27.55</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.4">
+        <v>37.340000000000003</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C70">
-        <v>271.49</v>
+        <v>524.79999999999995</v>
       </c>
       <c r="D70">
-        <v>6.1</v>
+        <v>7.11</v>
       </c>
       <c r="E70">
-        <v>6.38</v>
-      </c>
-      <c r="F70" t="s">
-        <v>76</v>
+        <v>11.72</v>
+      </c>
+      <c r="F70">
+        <v>7.59</v>
       </c>
       <c r="G70">
-        <v>32.979999999999997</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.4">
+        <v>75.72</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C71">
-        <v>268.68</v>
+        <v>196.44</v>
       </c>
       <c r="D71">
-        <v>6.2</v>
+        <v>8.85</v>
       </c>
       <c r="E71">
-        <v>14.03</v>
+        <v>10.65</v>
       </c>
       <c r="F71">
-        <v>9.16</v>
+        <v>6.05</v>
       </c>
       <c r="G71">
-        <v>33.549999999999997</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.4">
+        <v>69.28</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>78</v>
-      </c>
-      <c r="C72">
-        <v>257.04000000000002</v>
+        <v>83</v>
+      </c>
+      <c r="C72" s="1">
+        <v>1095.25</v>
       </c>
       <c r="D72">
-        <v>7.8</v>
+        <v>5.97</v>
       </c>
       <c r="E72">
-        <v>14.12</v>
+        <v>10.63</v>
       </c>
       <c r="F72">
-        <v>8.34</v>
+        <v>7.6</v>
       </c>
       <c r="G72">
-        <v>33.61</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.4">
+        <v>46.23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C73">
-        <v>249.38</v>
+        <v>506.55</v>
       </c>
       <c r="D73">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="E73">
-        <v>7.81</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="F73">
-        <v>5.76</v>
+        <v>7.51</v>
       </c>
       <c r="G73">
-        <v>29.99</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.4">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C74">
-        <v>248.02</v>
+        <v>594.29999999999995</v>
       </c>
       <c r="D74">
-        <v>7.6</v>
+        <v>6.32</v>
       </c>
       <c r="E74">
-        <v>8.9499999999999993</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="F74">
-        <v>5.04</v>
+        <v>7.69</v>
       </c>
       <c r="G74">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.4">
+        <v>33.85</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C75">
-        <v>236.75</v>
+        <v>354.03</v>
       </c>
       <c r="D75">
-        <v>1.9</v>
+        <v>7.45</v>
       </c>
       <c r="E75">
-        <v>7.87</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="F75">
-        <v>5.41</v>
+        <v>3.99</v>
       </c>
       <c r="G75">
-        <v>25.38</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.4">
+        <v>72.52</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C76">
-        <v>226.64</v>
+        <v>144.96</v>
       </c>
       <c r="D76">
-        <v>7.3</v>
+        <v>6.43</v>
       </c>
       <c r="E76">
-        <v>7.01</v>
+        <v>9.4</v>
       </c>
       <c r="F76">
-        <v>5.3</v>
+        <v>7.72</v>
       </c>
       <c r="G76">
-        <v>29.75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.4">
+        <v>17.690000000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C77">
-        <v>224.68</v>
+        <v>408.24</v>
       </c>
       <c r="D77">
-        <v>7.6</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="E77">
-        <v>9.82</v>
+        <v>9.31</v>
       </c>
       <c r="F77">
-        <v>6.51</v>
+        <v>4.99</v>
       </c>
       <c r="G77">
-        <v>25.15</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.4">
+        <v>47.87</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C78">
-        <v>223.43</v>
+        <v>171.62</v>
       </c>
       <c r="D78">
-        <v>6.4</v>
+        <v>5.83</v>
       </c>
       <c r="E78">
-        <v>8.34</v>
+        <v>9</v>
       </c>
       <c r="F78">
-        <v>5.24</v>
+        <v>3.35</v>
       </c>
       <c r="G78">
-        <v>29.73</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.4">
+        <v>36.549999999999997</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C79">
-        <v>204.4</v>
+        <v>137.22999999999999</v>
       </c>
       <c r="D79">
-        <v>3.5</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="E79">
-        <v>11.36</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F79">
-        <v>7.75</v>
+        <v>3.91</v>
       </c>
       <c r="G79">
-        <v>21.84</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.4">
+        <v>41.07</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C80">
-        <v>190.74</v>
+        <v>129.35</v>
       </c>
       <c r="D80">
-        <v>8.1</v>
+        <v>14.59</v>
       </c>
       <c r="E80">
-        <v>5.95</v>
+        <v>7.98</v>
       </c>
       <c r="F80">
-        <v>4.03</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="G80">
-        <v>13.91</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.4">
+        <v>34.68</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C81">
-        <v>181.74</v>
+        <v>123.25</v>
       </c>
       <c r="D81">
-        <v>6.6</v>
+        <v>2.7</v>
       </c>
       <c r="E81">
-        <v>7.26</v>
+        <v>7.92</v>
       </c>
       <c r="F81">
-        <v>4.83</v>
+        <v>4.32</v>
       </c>
       <c r="G81">
-        <v>31.64</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C82">
-        <v>180.48</v>
+        <v>287.33999999999997</v>
       </c>
       <c r="D82">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="E82">
-        <v>7.01</v>
+        <v>7.28</v>
       </c>
       <c r="F82">
-        <v>4.57</v>
+        <v>4.97</v>
       </c>
       <c r="G82">
-        <v>19.809999999999999</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.4">
+        <v>26.31</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C83">
-        <v>156.94999999999999</v>
+        <v>279.94</v>
       </c>
       <c r="D83">
-        <v>-1.2</v>
+        <v>12.24</v>
       </c>
       <c r="E83">
-        <v>4.51</v>
+        <v>7.26</v>
       </c>
       <c r="F83">
-        <v>3.58</v>
+        <v>4.18</v>
       </c>
       <c r="G83">
-        <v>16.57</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.4">
+        <v>54.08</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C84">
-        <v>151.18</v>
+        <v>216.09</v>
       </c>
       <c r="D84">
-        <v>4.4000000000000004</v>
+        <v>8.42</v>
       </c>
       <c r="E84">
-        <v>3.04</v>
+        <v>7.22</v>
       </c>
       <c r="F84">
-        <v>2.06</v>
+        <v>5.07</v>
       </c>
       <c r="G84">
-        <v>18.47</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.4">
+        <v>26.21</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C85">
-        <v>140.62</v>
+        <v>427.8</v>
       </c>
       <c r="D85">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E85">
-        <v>5.71</v>
+        <v>7.2</v>
       </c>
       <c r="F85">
-        <v>4.0999999999999996</v>
+        <v>5.46</v>
       </c>
       <c r="G85">
-        <v>23.72</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.4">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C86">
-        <v>121.85</v>
+        <v>176.22</v>
       </c>
       <c r="D86">
-        <v>6.2</v>
+        <v>7.98</v>
       </c>
       <c r="E86">
-        <v>3.59</v>
+        <v>7.17</v>
       </c>
       <c r="F86">
-        <v>2.54</v>
+        <v>3.21</v>
       </c>
       <c r="G86">
-        <v>14.34</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.4">
+        <v>34.56</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C87">
-        <v>120.47</v>
+        <v>109.19</v>
       </c>
       <c r="D87">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="E87">
-        <v>4.7</v>
+        <v>7.02</v>
       </c>
       <c r="F87">
-        <v>3.37</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="G87">
-        <v>16.21</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.4">
+        <v>24.62</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C88">
-        <v>110.75</v>
+        <v>131.05000000000001</v>
       </c>
       <c r="D88">
-        <v>5.0999999999999996</v>
+        <v>6.71</v>
       </c>
       <c r="E88">
-        <v>3.51</v>
+        <v>6.89</v>
       </c>
       <c r="F88">
-        <v>2.2599999999999998</v>
+        <v>3.96</v>
       </c>
       <c r="G88">
-        <v>19.98</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.4">
+        <v>39.520000000000003</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C89">
-        <v>105.51</v>
+        <v>636.69000000000005</v>
       </c>
       <c r="D89">
-        <v>13.5</v>
+        <v>39.729999999999997</v>
       </c>
       <c r="E89">
-        <v>4.01</v>
+        <v>6.58</v>
       </c>
       <c r="F89">
-        <v>2.95</v>
+        <v>5.17</v>
       </c>
       <c r="G89">
-        <v>21.68</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.4">
+        <v>18.53</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C90">
-        <v>104.5</v>
+        <v>100.38</v>
       </c>
       <c r="D90">
-        <v>7.9</v>
+        <v>6.75</v>
       </c>
       <c r="E90">
-        <v>4.1500000000000004</v>
+        <v>6.52</v>
       </c>
       <c r="F90">
-        <v>2.93</v>
+        <v>3.34</v>
       </c>
       <c r="G90">
-        <v>19.690000000000001</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.4">
+        <v>45.36</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C91">
-        <v>102.16</v>
+        <v>185.45</v>
       </c>
       <c r="D91">
-        <v>-3.8</v>
+        <v>6.8</v>
       </c>
       <c r="E91">
-        <v>2.94</v>
+        <v>6.33</v>
       </c>
       <c r="F91">
-        <v>1.9</v>
+        <v>4.26</v>
       </c>
       <c r="G91">
-        <v>15.15</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.4">
+        <v>21.39</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C92">
-        <v>90.12</v>
+        <v>305.61</v>
       </c>
       <c r="D92">
-        <v>14.3</v>
+        <v>4.97</v>
       </c>
       <c r="E92">
-        <v>3.95</v>
+        <v>6.15</v>
       </c>
       <c r="F92">
-        <v>2.39</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="G92">
-        <v>19.2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.4">
+        <v>19.66</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C93">
-        <v>85.54</v>
+        <v>109.44</v>
       </c>
       <c r="D93">
-        <v>5.8</v>
+        <v>14.32</v>
       </c>
       <c r="E93">
-        <v>2.81</v>
+        <v>6.13</v>
       </c>
       <c r="F93">
-        <v>1.53</v>
+        <v>4.01</v>
       </c>
       <c r="G93">
-        <v>14.06</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.4">
+        <v>29.04</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C94">
-        <v>77.819999999999993</v>
+        <v>85.85</v>
       </c>
       <c r="D94">
-        <v>0.5</v>
+        <v>5.95</v>
       </c>
       <c r="E94">
-        <v>3.4</v>
+        <v>5.28</v>
       </c>
       <c r="F94">
-        <v>2.68</v>
+        <v>2.35</v>
       </c>
       <c r="G94">
-        <v>13.89</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.4">
+        <v>29.05</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>101</v>
-      </c>
-      <c r="C95" t="s">
-        <v>76</v>
-      </c>
-      <c r="D95" t="s">
-        <v>76</v>
-      </c>
-      <c r="E95" t="s">
-        <v>76</v>
-      </c>
-      <c r="F95" t="s">
-        <v>76</v>
-      </c>
-      <c r="G95" t="s">
-        <v>76</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C95">
+        <v>98.64</v>
+      </c>
+      <c r="D95">
+        <v>13.98</v>
+      </c>
+      <c r="E95">
+        <v>5.05</v>
+      </c>
+      <c r="F95">
+        <v>2.41</v>
+      </c>
+      <c r="G95">
+        <v>25.43</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>107</v>
+      </c>
+      <c r="C96">
+        <v>227.09</v>
+      </c>
+      <c r="D96">
+        <v>2.5</v>
+      </c>
+      <c r="E96">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F96">
+        <v>3.86</v>
+      </c>
+      <c r="G96">
+        <v>19.190000000000001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>108</v>
+      </c>
+      <c r="C97">
+        <v>81.89</v>
+      </c>
+      <c r="D97">
+        <v>9.06</v>
+      </c>
+      <c r="E97">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="F97">
+        <v>2.78</v>
+      </c>
+      <c r="G97">
+        <v>25.97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>109</v>
+      </c>
+      <c r="C98">
+        <v>111.98</v>
+      </c>
+      <c r="D98">
+        <v>8.61</v>
+      </c>
+      <c r="E98">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="F98">
+        <v>3.42</v>
+      </c>
+      <c r="G98">
+        <v>25.79</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>110</v>
+      </c>
+      <c r="C99">
+        <v>350.86</v>
+      </c>
+      <c r="D99">
+        <v>3.27</v>
+      </c>
+      <c r="E99">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="F99">
+        <v>4.04</v>
+      </c>
+      <c r="G99">
+        <v>21.94</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>111</v>
+      </c>
+      <c r="C100">
+        <v>355.04</v>
+      </c>
+      <c r="D100">
+        <v>7.05</v>
+      </c>
+      <c r="E100">
+        <v>3.38</v>
+      </c>
+      <c r="F100">
+        <v>2.73</v>
+      </c>
+      <c r="G100">
+        <v>14.24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>112</v>
+      </c>
+      <c r="C101">
+        <v>35.020000000000003</v>
+      </c>
+      <c r="D101">
+        <v>5.96</v>
+      </c>
+      <c r="E101">
+        <v>2.41</v>
+      </c>
+      <c r="F101">
+        <v>1.76</v>
+      </c>
+      <c r="G101">
+        <v>13.84</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="1"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="1"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="1"/>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="1"/>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="1"/>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="1"/>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="1"/>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="1"/>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="1"/>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="1"/>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="1"/>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="1"/>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="1"/>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="1"/>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="1"/>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="1"/>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="1"/>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="1"/>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="1"/>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" s="1"/>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" s="1"/>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" s="1"/>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="1"/>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" s="1"/>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" s="1"/>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" s="1"/>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" s="1"/>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" s="1"/>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" s="1"/>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" s="1"/>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" s="1"/>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" s="1"/>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" s="1"/>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" s="1"/>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C88796F3-D80D-4751-BD49-76637E6564D8}">
+  <dimension ref="A1:E134"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>32</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>27</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>26</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>23</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>20</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>21</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>22</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>18</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>19</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>17</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>11</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>12</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>13</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <v>10</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>127577.42</v>
+      </c>
+      <c r="B35">
+        <v>8.27</v>
+      </c>
+      <c r="C35" s="1">
+        <v>14105.04</v>
+      </c>
+      <c r="D35" s="1">
+        <v>10785.23</v>
+      </c>
+      <c r="E35" s="1">
+        <v>18247.009999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>1588.24</v>
+      </c>
+      <c r="B36">
+        <v>7.9</v>
+      </c>
+      <c r="C36">
+        <v>64.28</v>
+      </c>
+      <c r="D36">
+        <v>56.08</v>
+      </c>
+      <c r="E36">
+        <v>83.59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>2532.84</v>
+      </c>
+      <c r="B37">
+        <v>7.95</v>
+      </c>
+      <c r="C37">
+        <v>69.42</v>
+      </c>
+      <c r="D37">
+        <v>47.78</v>
+      </c>
+      <c r="E37">
+        <v>192.35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>1407.2</v>
+      </c>
+      <c r="B38">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="C38">
+        <v>71.52</v>
+      </c>
+      <c r="D38">
+        <v>49.64</v>
+      </c>
+      <c r="E38">
+        <v>81.67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>1348.43</v>
+      </c>
+      <c r="B39">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="C39">
+        <v>78.819999999999993</v>
+      </c>
+      <c r="D39">
+        <v>75.06</v>
+      </c>
+      <c r="E39">
+        <v>182.37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>6004.16</v>
+      </c>
+      <c r="B40">
+        <v>8.16</v>
+      </c>
+      <c r="C40">
+        <v>77.760000000000005</v>
+      </c>
+      <c r="D40">
+        <v>61.3</v>
+      </c>
+      <c r="E40">
+        <v>160.56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>1802.98</v>
+      </c>
+      <c r="B41">
+        <v>6.57</v>
+      </c>
+      <c r="C41">
+        <v>86.27</v>
+      </c>
+      <c r="D41">
+        <v>60.51</v>
+      </c>
+      <c r="E41">
+        <v>170.96</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>2657.7</v>
+      </c>
+      <c r="B42">
+        <v>9.02</v>
+      </c>
+      <c r="C42">
+        <v>107.67</v>
+      </c>
+      <c r="D42">
+        <v>81.290000000000006</v>
+      </c>
+      <c r="E42">
+        <v>195.38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>2508.23</v>
+      </c>
+      <c r="B43">
+        <v>6.14</v>
+      </c>
+      <c r="C43">
+        <v>107.29</v>
+      </c>
+      <c r="D43">
+        <v>102.21</v>
+      </c>
+      <c r="E43">
+        <v>183.25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>1362.04</v>
+      </c>
+      <c r="B44">
+        <v>5.9</v>
+      </c>
+      <c r="C44">
+        <v>95.01</v>
+      </c>
+      <c r="D44">
+        <v>57.8</v>
+      </c>
+      <c r="E44">
+        <v>443.07</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>2153.65</v>
+      </c>
+      <c r="B45">
+        <v>9.64</v>
+      </c>
+      <c r="C45">
+        <v>108.2</v>
+      </c>
+      <c r="D45">
+        <v>86.91</v>
+      </c>
+      <c r="E45">
+        <v>242.37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>2185.35</v>
+      </c>
+      <c r="B46">
+        <v>8.5</v>
+      </c>
+      <c r="C46">
+        <v>119.74</v>
+      </c>
+      <c r="D46">
+        <v>85.96</v>
+      </c>
+      <c r="E46">
+        <v>136.58000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>1255.3599999999999</v>
+      </c>
+      <c r="B47">
+        <v>10.66</v>
+      </c>
+      <c r="C47">
+        <v>113.85</v>
+      </c>
+      <c r="D47">
+        <v>96.86</v>
+      </c>
+      <c r="E47">
+        <v>156.52000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>1560.26</v>
+      </c>
+      <c r="B48">
+        <v>8.67</v>
+      </c>
+      <c r="C48">
+        <v>109.08</v>
+      </c>
+      <c r="D48">
+        <v>59.34</v>
+      </c>
+      <c r="E48">
+        <v>370.19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>2719.29</v>
+      </c>
+      <c r="B49">
+        <v>10.81</v>
+      </c>
+      <c r="C49">
+        <v>146.46</v>
+      </c>
+      <c r="D49">
+        <v>90.33</v>
+      </c>
+      <c r="E49">
+        <v>396.8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>2982.2</v>
+      </c>
+      <c r="B50">
+        <v>6.54</v>
+      </c>
+      <c r="C50">
+        <v>146.35</v>
+      </c>
+      <c r="D50">
+        <v>103.51</v>
+      </c>
+      <c r="E50">
+        <v>412.92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>4187.8900000000003</v>
+      </c>
+      <c r="B51">
+        <v>8.17</v>
+      </c>
+      <c r="C51">
+        <v>206.82</v>
+      </c>
+      <c r="D51">
+        <v>166.91</v>
+      </c>
+      <c r="E51">
+        <v>357.92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>3615.7</v>
+      </c>
+      <c r="B52">
+        <v>8.77</v>
+      </c>
+      <c r="C52">
+        <v>160.4</v>
+      </c>
+      <c r="D52">
+        <v>97.89</v>
+      </c>
+      <c r="E52">
+        <v>547.39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>2807.32</v>
+      </c>
+      <c r="B53">
+        <v>9.84</v>
+      </c>
+      <c r="C53">
+        <v>152.21</v>
+      </c>
+      <c r="D53">
+        <v>141.16999999999999</v>
+      </c>
+      <c r="E53">
+        <v>292.31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>3761.42</v>
+      </c>
+      <c r="B54">
+        <v>7.67</v>
+      </c>
+      <c r="C54">
+        <v>148.41</v>
+      </c>
+      <c r="D54">
+        <v>83</v>
+      </c>
+      <c r="E54">
+        <v>489.54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>4128.09</v>
+      </c>
+      <c r="B55">
+        <v>8.5</v>
+      </c>
+      <c r="C55">
+        <v>274.01</v>
+      </c>
+      <c r="D55">
+        <v>196.91</v>
+      </c>
+      <c r="E55">
+        <v>265.77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>3565.66</v>
+      </c>
+      <c r="B56">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="C56">
+        <v>266.57</v>
+      </c>
+      <c r="D56">
+        <v>183.16</v>
+      </c>
+      <c r="E56">
+        <v>289.42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>5319.86</v>
+      </c>
+      <c r="B57">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="C57">
+        <v>214.29</v>
+      </c>
+      <c r="D57">
+        <v>204.25</v>
+      </c>
+      <c r="E57">
+        <v>296.29000000000002</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>3997.86</v>
+      </c>
+      <c r="B58">
+        <v>7.52</v>
+      </c>
+      <c r="C58">
+        <v>448.19</v>
+      </c>
+      <c r="D58">
+        <v>314.14</v>
+      </c>
+      <c r="E58">
+        <v>786.66</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>7708.74</v>
+      </c>
+      <c r="B59">
+        <v>9.56</v>
+      </c>
+      <c r="C59">
+        <v>361.02</v>
+      </c>
+      <c r="D59">
+        <v>351.5</v>
+      </c>
+      <c r="E59">
+        <v>402.42</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>4419.0600000000004</v>
+      </c>
+      <c r="B60">
+        <v>11.25</v>
+      </c>
+      <c r="C60">
+        <v>296</v>
+      </c>
+      <c r="D60">
+        <v>290.69</v>
+      </c>
+      <c r="E60">
+        <v>452.16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>4968.6099999999997</v>
+      </c>
+      <c r="B61">
+        <v>-5.36</v>
+      </c>
+      <c r="C61">
+        <v>292.22000000000003</v>
+      </c>
+      <c r="D61">
+        <v>259.83</v>
+      </c>
+      <c r="E61">
+        <v>380.71</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>3695.31</v>
+      </c>
+      <c r="B62">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="C62">
+        <v>279.87</v>
+      </c>
+      <c r="D62">
+        <v>176.89</v>
+      </c>
+      <c r="E62">
+        <v>460.25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>12349.22</v>
+      </c>
+      <c r="B63">
+        <v>8.61</v>
+      </c>
+      <c r="C63">
+        <v>808.26</v>
+      </c>
+      <c r="D63">
+        <v>545.71</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1072.01</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>5259.64</v>
+      </c>
+      <c r="B64">
+        <v>10.83</v>
+      </c>
+      <c r="C64">
+        <v>455.39</v>
+      </c>
+      <c r="D64">
+        <v>335.02</v>
+      </c>
+      <c r="E64">
+        <v>663.31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>31473.84</v>
+      </c>
+      <c r="B65">
+        <v>7.26</v>
+      </c>
+      <c r="C65" s="1">
+        <v>4257.7</v>
+      </c>
+      <c r="D65" s="1">
+        <v>3450.41</v>
+      </c>
+      <c r="E65" s="1">
+        <v>4570.22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>28848.959999999999</v>
+      </c>
+      <c r="B66">
+        <v>8.32</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1884.26</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1410.06</v>
+      </c>
+      <c r="E66" s="1">
+        <v>3021.18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B67" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B70">
+        <v>33</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B71">
+        <v>32</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B72">
+        <v>31</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B73">
+        <v>30</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B74">
+        <v>28</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B75">
+        <v>29</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B76">
+        <v>27</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B77">
+        <v>24</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B78">
+        <v>25</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B79">
+        <v>26</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B80">
+        <v>23</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B81">
+        <v>20</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B82">
+        <v>21</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B83">
+        <v>22</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B84">
+        <v>18</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B85">
+        <v>19</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B86">
+        <v>14</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B87">
+        <v>15</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B88">
+        <v>16</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B89">
+        <v>17</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B90">
+        <v>11</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B91">
+        <v>12</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B92">
+        <v>13</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B93">
+        <v>6</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B94">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B95">
+        <v>8</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B96">
+        <v>9</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B97">
+        <v>10</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B98">
+        <v>4</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B99">
+        <v>5</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B100">
+        <v>2</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B101">
+        <v>3</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>127577.42</v>
+      </c>
+      <c r="B102">
+        <v>8.27</v>
+      </c>
+      <c r="C102" s="1">
+        <v>14105.04</v>
+      </c>
+      <c r="D102" s="1">
+        <v>10785.23</v>
+      </c>
+      <c r="E102" s="1">
+        <v>18247.009999999998</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>910.09</v>
+      </c>
+      <c r="B103">
+        <v>11.69</v>
+      </c>
+      <c r="C103">
+        <v>64.03</v>
+      </c>
+      <c r="D103">
+        <v>61.97</v>
+      </c>
+      <c r="E103">
+        <v>157.85</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>1588.24</v>
+      </c>
+      <c r="B104">
+        <v>7.9</v>
+      </c>
+      <c r="C104">
+        <v>64.28</v>
+      </c>
+      <c r="D104">
+        <v>56.08</v>
+      </c>
+      <c r="E104">
+        <v>83.59</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>2532.84</v>
+      </c>
+      <c r="B105">
+        <v>7.95</v>
+      </c>
+      <c r="C105">
+        <v>69.42</v>
+      </c>
+      <c r="D105">
+        <v>47.78</v>
+      </c>
+      <c r="E105">
+        <v>192.35</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>1407.2</v>
+      </c>
+      <c r="B106">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="C106">
+        <v>71.52</v>
+      </c>
+      <c r="D106">
+        <v>49.64</v>
+      </c>
+      <c r="E106">
+        <v>81.67</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>1348.43</v>
+      </c>
+      <c r="B107">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="C107">
+        <v>78.819999999999993</v>
+      </c>
+      <c r="D107">
+        <v>75.06</v>
+      </c>
+      <c r="E107">
+        <v>182.37</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>6004.16</v>
+      </c>
+      <c r="B108">
+        <v>8.16</v>
+      </c>
+      <c r="C108">
+        <v>77.760000000000005</v>
+      </c>
+      <c r="D108">
+        <v>61.3</v>
+      </c>
+      <c r="E108">
+        <v>160.56</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>1802.98</v>
+      </c>
+      <c r="B109">
+        <v>6.57</v>
+      </c>
+      <c r="C109">
+        <v>86.27</v>
+      </c>
+      <c r="D109">
+        <v>60.51</v>
+      </c>
+      <c r="E109">
+        <v>170.96</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>2657.7</v>
+      </c>
+      <c r="B110">
+        <v>9.02</v>
+      </c>
+      <c r="C110">
+        <v>107.67</v>
+      </c>
+      <c r="D110">
+        <v>81.290000000000006</v>
+      </c>
+      <c r="E110">
+        <v>195.38</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>2508.23</v>
+      </c>
+      <c r="B111">
+        <v>6.14</v>
+      </c>
+      <c r="C111">
+        <v>107.29</v>
+      </c>
+      <c r="D111">
+        <v>102.21</v>
+      </c>
+      <c r="E111">
+        <v>183.25</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>1362.04</v>
+      </c>
+      <c r="B112">
+        <v>5.9</v>
+      </c>
+      <c r="C112">
+        <v>95.01</v>
+      </c>
+      <c r="D112">
+        <v>57.8</v>
+      </c>
+      <c r="E112">
+        <v>443.07</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>2153.65</v>
+      </c>
+      <c r="B113">
+        <v>9.64</v>
+      </c>
+      <c r="C113">
+        <v>108.2</v>
+      </c>
+      <c r="D113">
+        <v>86.91</v>
+      </c>
+      <c r="E113">
+        <v>242.37</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>2185.35</v>
+      </c>
+      <c r="B114">
+        <v>8.5</v>
+      </c>
+      <c r="C114">
+        <v>119.74</v>
+      </c>
+      <c r="D114">
+        <v>85.96</v>
+      </c>
+      <c r="E114">
+        <v>136.58000000000001</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>1255.3599999999999</v>
+      </c>
+      <c r="B115">
+        <v>10.66</v>
+      </c>
+      <c r="C115">
+        <v>113.85</v>
+      </c>
+      <c r="D115">
+        <v>96.86</v>
+      </c>
+      <c r="E115">
+        <v>156.52000000000001</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>1560.26</v>
+      </c>
+      <c r="B116">
+        <v>8.67</v>
+      </c>
+      <c r="C116">
+        <v>109.08</v>
+      </c>
+      <c r="D116">
+        <v>59.34</v>
+      </c>
+      <c r="E116">
+        <v>370.19</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>2719.29</v>
+      </c>
+      <c r="B117">
+        <v>10.81</v>
+      </c>
+      <c r="C117">
+        <v>146.46</v>
+      </c>
+      <c r="D117">
+        <v>90.33</v>
+      </c>
+      <c r="E117">
+        <v>396.8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>2982.2</v>
+      </c>
+      <c r="B118">
+        <v>6.54</v>
+      </c>
+      <c r="C118">
+        <v>146.35</v>
+      </c>
+      <c r="D118">
+        <v>103.51</v>
+      </c>
+      <c r="E118">
+        <v>412.92</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>4187.8900000000003</v>
+      </c>
+      <c r="B119">
+        <v>8.17</v>
+      </c>
+      <c r="C119">
+        <v>206.82</v>
+      </c>
+      <c r="D119">
+        <v>166.91</v>
+      </c>
+      <c r="E119">
+        <v>357.92</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>3615.7</v>
+      </c>
+      <c r="B120">
+        <v>8.77</v>
+      </c>
+      <c r="C120">
+        <v>160.4</v>
+      </c>
+      <c r="D120">
+        <v>97.89</v>
+      </c>
+      <c r="E120">
+        <v>547.39</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>2807.32</v>
+      </c>
+      <c r="B121">
+        <v>9.84</v>
+      </c>
+      <c r="C121">
+        <v>152.21</v>
+      </c>
+      <c r="D121">
+        <v>141.16999999999999</v>
+      </c>
+      <c r="E121">
+        <v>292.31</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>3761.42</v>
+      </c>
+      <c r="B122">
+        <v>7.67</v>
+      </c>
+      <c r="C122">
+        <v>148.41</v>
+      </c>
+      <c r="D122">
+        <v>83</v>
+      </c>
+      <c r="E122">
+        <v>489.54</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>4128.09</v>
+      </c>
+      <c r="B123">
+        <v>8.5</v>
+      </c>
+      <c r="C123">
+        <v>274.01</v>
+      </c>
+      <c r="D123">
+        <v>196.91</v>
+      </c>
+      <c r="E123">
+        <v>265.77</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>3565.66</v>
+      </c>
+      <c r="B124">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="C124">
+        <v>266.57</v>
+      </c>
+      <c r="D124">
+        <v>183.16</v>
+      </c>
+      <c r="E124">
+        <v>289.42</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>5319.86</v>
+      </c>
+      <c r="B125">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="C125">
+        <v>214.29</v>
+      </c>
+      <c r="D125">
+        <v>204.25</v>
+      </c>
+      <c r="E125">
+        <v>296.29000000000002</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>3997.86</v>
+      </c>
+      <c r="B126">
+        <v>7.52</v>
+      </c>
+      <c r="C126">
+        <v>448.19</v>
+      </c>
+      <c r="D126">
+        <v>314.14</v>
+      </c>
+      <c r="E126">
+        <v>786.66</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>7708.74</v>
+      </c>
+      <c r="B127">
+        <v>9.56</v>
+      </c>
+      <c r="C127">
+        <v>361.02</v>
+      </c>
+      <c r="D127">
+        <v>351.5</v>
+      </c>
+      <c r="E127">
+        <v>402.42</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>4419.0600000000004</v>
+      </c>
+      <c r="B128">
+        <v>11.25</v>
+      </c>
+      <c r="C128">
+        <v>296</v>
+      </c>
+      <c r="D128">
+        <v>290.69</v>
+      </c>
+      <c r="E128">
+        <v>452.16</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>4968.6099999999997</v>
+      </c>
+      <c r="B129">
+        <v>-5.36</v>
+      </c>
+      <c r="C129">
+        <v>292.22000000000003</v>
+      </c>
+      <c r="D129">
+        <v>259.83</v>
+      </c>
+      <c r="E129">
+        <v>380.71</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>3695.31</v>
+      </c>
+      <c r="B130">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="C130">
+        <v>279.87</v>
+      </c>
+      <c r="D130">
+        <v>176.89</v>
+      </c>
+      <c r="E130">
+        <v>460.25</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>12349.22</v>
+      </c>
+      <c r="B131">
+        <v>8.61</v>
+      </c>
+      <c r="C131">
+        <v>808.26</v>
+      </c>
+      <c r="D131">
+        <v>545.71</v>
+      </c>
+      <c r="E131" s="1">
+        <v>1072.01</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>5259.64</v>
+      </c>
+      <c r="B132">
+        <v>10.83</v>
+      </c>
+      <c r="C132">
+        <v>455.39</v>
+      </c>
+      <c r="D132">
+        <v>335.02</v>
+      </c>
+      <c r="E132">
+        <v>663.31</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>31473.84</v>
+      </c>
+      <c r="B133">
+        <v>7.26</v>
+      </c>
+      <c r="C133" s="1">
+        <v>4257.7</v>
+      </c>
+      <c r="D133" s="1">
+        <v>3450.41</v>
+      </c>
+      <c r="E133" s="1">
+        <v>4570.22</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>28848.959999999999</v>
+      </c>
+      <c r="B134">
+        <v>8.32</v>
+      </c>
+      <c r="C134" s="1">
+        <v>1884.26</v>
+      </c>
+      <c r="D134" s="1">
+        <v>1410.06</v>
+      </c>
+      <c r="E134" s="1">
+        <v>3021.18</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9089FCE8-94BE-4C55-95AB-3EB98495740A}">
+  <dimension ref="B1:H67"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1">
+        <v>127577.42</v>
+      </c>
+      <c r="E2">
+        <v>8.27</v>
+      </c>
+      <c r="F2" s="1">
+        <v>14105.04</v>
+      </c>
+      <c r="G2" s="1">
+        <v>10785.23</v>
+      </c>
+      <c r="H2" s="1">
+        <v>18247.009999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="1">
+        <v>31473.84</v>
+      </c>
+      <c r="E3">
+        <v>7.26</v>
+      </c>
+      <c r="F3" s="1">
+        <v>4257.7</v>
+      </c>
+      <c r="G3" s="1">
+        <v>3450.41</v>
+      </c>
+      <c r="H3" s="1">
+        <v>4570.22</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="1">
+        <v>28848.959999999999</v>
+      </c>
+      <c r="E4">
+        <v>8.32</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1884.26</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1410.06</v>
+      </c>
+      <c r="H4" s="1">
+        <v>3021.18</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="1">
+        <v>12349.22</v>
+      </c>
+      <c r="E5">
+        <v>8.61</v>
+      </c>
+      <c r="F5">
+        <v>808.26</v>
+      </c>
+      <c r="G5">
+        <v>545.71</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1072.01</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5259.64</v>
+      </c>
+      <c r="E6">
+        <v>10.83</v>
+      </c>
+      <c r="F6">
+        <v>455.39</v>
+      </c>
+      <c r="G6">
+        <v>335.02</v>
+      </c>
+      <c r="H6">
+        <v>663.31</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3997.86</v>
+      </c>
+      <c r="E7">
+        <v>7.52</v>
+      </c>
+      <c r="F7">
+        <v>448.19</v>
+      </c>
+      <c r="G7">
+        <v>314.14</v>
+      </c>
+      <c r="H7">
+        <v>786.66</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1">
+        <v>7708.74</v>
+      </c>
+      <c r="E8">
+        <v>9.56</v>
+      </c>
+      <c r="F8">
+        <v>361.02</v>
+      </c>
+      <c r="G8">
+        <v>351.5</v>
+      </c>
+      <c r="H8">
+        <v>402.42</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4419.0600000000004</v>
+      </c>
+      <c r="E9">
+        <v>11.25</v>
+      </c>
+      <c r="F9">
+        <v>296</v>
+      </c>
+      <c r="G9">
+        <v>290.69</v>
+      </c>
+      <c r="H9">
+        <v>452.16</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="1">
+        <v>4968.6099999999997</v>
+      </c>
+      <c r="E10">
+        <v>-5.36</v>
+      </c>
+      <c r="F10">
+        <v>292.22000000000003</v>
+      </c>
+      <c r="G10">
+        <v>259.83</v>
+      </c>
+      <c r="H10">
+        <v>380.71</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3695.31</v>
+      </c>
+      <c r="E11">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="F11">
+        <v>279.87</v>
+      </c>
+      <c r="G11">
+        <v>176.89</v>
+      </c>
+      <c r="H11">
+        <v>460.25</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="1">
+        <v>4128.09</v>
+      </c>
+      <c r="E12">
+        <v>8.5</v>
+      </c>
+      <c r="F12">
+        <v>274.01</v>
+      </c>
+      <c r="G12">
+        <v>196.91</v>
+      </c>
+      <c r="H12">
+        <v>265.77</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3565.66</v>
+      </c>
+      <c r="E13">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="F13">
+        <v>266.57</v>
+      </c>
+      <c r="G13">
+        <v>183.16</v>
+      </c>
+      <c r="H13">
+        <v>289.42</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="1">
+        <v>5319.86</v>
+      </c>
+      <c r="E14">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="F14">
+        <v>214.29</v>
+      </c>
+      <c r="G14">
+        <v>204.25</v>
+      </c>
+      <c r="H14">
+        <v>296.29000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="1">
+        <v>4187.8900000000003</v>
+      </c>
+      <c r="E15">
+        <v>8.17</v>
+      </c>
+      <c r="F15">
+        <v>206.82</v>
+      </c>
+      <c r="G15">
+        <v>166.91</v>
+      </c>
+      <c r="H15">
+        <v>357.92</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3615.7</v>
+      </c>
+      <c r="E16">
+        <v>8.77</v>
+      </c>
+      <c r="F16">
+        <v>160.4</v>
+      </c>
+      <c r="G16">
+        <v>97.89</v>
+      </c>
+      <c r="H16">
+        <v>547.39</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2807.32</v>
+      </c>
+      <c r="E17">
+        <v>9.84</v>
+      </c>
+      <c r="F17">
+        <v>152.21</v>
+      </c>
+      <c r="G17">
+        <v>141.16999999999999</v>
+      </c>
+      <c r="H17">
+        <v>292.31</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3761.42</v>
+      </c>
+      <c r="E18">
+        <v>7.67</v>
+      </c>
+      <c r="F18">
+        <v>148.41</v>
+      </c>
+      <c r="G18">
+        <v>83</v>
+      </c>
+      <c r="H18">
+        <v>489.54</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2719.29</v>
+      </c>
+      <c r="E19">
+        <v>10.81</v>
+      </c>
+      <c r="F19">
+        <v>146.46</v>
+      </c>
+      <c r="G19">
+        <v>90.33</v>
+      </c>
+      <c r="H19">
+        <v>396.8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2982.2</v>
+      </c>
+      <c r="E20">
+        <v>6.54</v>
+      </c>
+      <c r="F20">
+        <v>146.35</v>
+      </c>
+      <c r="G20">
+        <v>103.51</v>
+      </c>
+      <c r="H20">
+        <v>412.92</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2185.35</v>
+      </c>
+      <c r="E21">
+        <v>8.5</v>
+      </c>
+      <c r="F21">
+        <v>119.74</v>
+      </c>
+      <c r="G21">
+        <v>85.96</v>
+      </c>
+      <c r="H21">
+        <v>136.58000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1255.3599999999999</v>
+      </c>
+      <c r="E22">
+        <v>10.66</v>
+      </c>
+      <c r="F22">
+        <v>113.85</v>
+      </c>
+      <c r="G22">
+        <v>96.86</v>
+      </c>
+      <c r="H22">
+        <v>156.52000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1560.26</v>
+      </c>
+      <c r="E23">
+        <v>8.67</v>
+      </c>
+      <c r="F23">
+        <v>109.08</v>
+      </c>
+      <c r="G23">
+        <v>59.34</v>
+      </c>
+      <c r="H23">
+        <v>370.19</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>23</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2153.65</v>
+      </c>
+      <c r="E24">
+        <v>9.64</v>
+      </c>
+      <c r="F24">
+        <v>108.2</v>
+      </c>
+      <c r="G24">
+        <v>86.91</v>
+      </c>
+      <c r="H24">
+        <v>242.37</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2657.7</v>
+      </c>
+      <c r="E25">
+        <v>9.02</v>
+      </c>
+      <c r="F25">
+        <v>107.67</v>
+      </c>
+      <c r="G25">
+        <v>81.290000000000006</v>
+      </c>
+      <c r="H25">
+        <v>195.38</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>25</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2508.23</v>
+      </c>
+      <c r="E27">
+        <v>6.14</v>
+      </c>
+      <c r="F27">
+        <v>107.29</v>
+      </c>
+      <c r="G27">
+        <v>102.21</v>
+      </c>
+      <c r="H27">
+        <v>183.25</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <v>26</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1362.04</v>
+      </c>
+      <c r="E28">
+        <v>5.9</v>
+      </c>
+      <c r="F28">
+        <v>95.01</v>
+      </c>
+      <c r="G28">
+        <v>57.8</v>
+      </c>
+      <c r="H28">
+        <v>443.07</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <v>27</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1802.98</v>
+      </c>
+      <c r="E29">
+        <v>6.57</v>
+      </c>
+      <c r="F29">
+        <v>86.27</v>
+      </c>
+      <c r="G29">
+        <v>60.51</v>
+      </c>
+      <c r="H29">
+        <v>170.96</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="1">
+        <v>127577.42</v>
+      </c>
+      <c r="E30">
+        <v>8.27</v>
+      </c>
+      <c r="F30" s="1">
+        <v>14105.04</v>
+      </c>
+      <c r="G30" s="1">
+        <v>10785.23</v>
+      </c>
+      <c r="H30" s="1">
+        <v>18247.009999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <v>28</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1348.43</v>
+      </c>
+      <c r="E31">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="F31">
+        <v>78.819999999999993</v>
+      </c>
+      <c r="G31">
+        <v>75.06</v>
+      </c>
+      <c r="H31">
+        <v>182.37</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="1">
+        <v>31473.84</v>
+      </c>
+      <c r="E32">
+        <v>7.26</v>
+      </c>
+      <c r="F32" s="1">
+        <v>4257.7</v>
+      </c>
+      <c r="G32" s="1">
+        <v>3450.41</v>
+      </c>
+      <c r="H32" s="1">
+        <v>4570.22</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <v>29</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="1">
+        <v>6004.16</v>
+      </c>
+      <c r="E33">
+        <v>8.16</v>
+      </c>
+      <c r="F33">
+        <v>77.760000000000005</v>
+      </c>
+      <c r="G33">
+        <v>61.3</v>
+      </c>
+      <c r="H33">
+        <v>160.56</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="1">
+        <v>28848.959999999999</v>
+      </c>
+      <c r="E34">
+        <v>8.32</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1884.26</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1410.06</v>
+      </c>
+      <c r="H34" s="1">
+        <v>3021.18</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <v>30</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1407.2</v>
+      </c>
+      <c r="E35">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F35">
+        <v>71.52</v>
+      </c>
+      <c r="G35">
+        <v>49.64</v>
+      </c>
+      <c r="H35">
+        <v>81.67</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <v>4</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="1">
+        <v>12349.22</v>
+      </c>
+      <c r="E36">
+        <v>8.61</v>
+      </c>
+      <c r="F36">
+        <v>808.26</v>
+      </c>
+      <c r="G36">
+        <v>545.71</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1072.01</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37">
+        <v>31</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2532.84</v>
+      </c>
+      <c r="E37">
+        <v>7.95</v>
+      </c>
+      <c r="F37">
+        <v>69.42</v>
+      </c>
+      <c r="G37">
+        <v>47.78</v>
+      </c>
+      <c r="H37">
+        <v>192.35</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="1">
+        <v>5259.64</v>
+      </c>
+      <c r="E38">
+        <v>10.83</v>
+      </c>
+      <c r="F38">
+        <v>455.39</v>
+      </c>
+      <c r="G38">
+        <v>335.02</v>
+      </c>
+      <c r="H38">
+        <v>663.31</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39">
+        <v>32</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1588.24</v>
+      </c>
+      <c r="E39">
+        <v>7.9</v>
+      </c>
+      <c r="F39">
+        <v>64.28</v>
+      </c>
+      <c r="G39">
+        <v>56.08</v>
+      </c>
+      <c r="H39">
+        <v>83.59</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40">
+        <v>6</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3997.86</v>
+      </c>
+      <c r="E40">
+        <v>7.52</v>
+      </c>
+      <c r="F40">
+        <v>448.19</v>
+      </c>
+      <c r="G40">
+        <v>314.14</v>
+      </c>
+      <c r="H40">
+        <v>786.66</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" s="1">
+        <v>7708.74</v>
+      </c>
+      <c r="E41">
+        <v>9.56</v>
+      </c>
+      <c r="F41">
+        <v>361.02</v>
+      </c>
+      <c r="G41">
+        <v>351.5</v>
+      </c>
+      <c r="H41">
+        <v>402.42</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" s="1">
+        <v>4419.0600000000004</v>
+      </c>
+      <c r="E42">
+        <v>11.25</v>
+      </c>
+      <c r="F42">
+        <v>296</v>
+      </c>
+      <c r="G42">
+        <v>290.69</v>
+      </c>
+      <c r="H42">
+        <v>452.16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <v>9</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="1">
+        <v>4968.6099999999997</v>
+      </c>
+      <c r="E43">
+        <v>-5.36</v>
+      </c>
+      <c r="F43">
+        <v>292.22000000000003</v>
+      </c>
+      <c r="G43">
+        <v>259.83</v>
+      </c>
+      <c r="H43">
+        <v>380.71</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44">
+        <v>10</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" s="1">
+        <v>3695.31</v>
+      </c>
+      <c r="E44">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="F44">
+        <v>279.87</v>
+      </c>
+      <c r="G44">
+        <v>176.89</v>
+      </c>
+      <c r="H44">
+        <v>460.25</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B45">
+        <v>11</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="1">
+        <v>4128.09</v>
+      </c>
+      <c r="E45">
+        <v>8.5</v>
+      </c>
+      <c r="F45">
+        <v>274.01</v>
+      </c>
+      <c r="G45">
+        <v>196.91</v>
+      </c>
+      <c r="H45">
+        <v>265.77</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B46">
+        <v>12</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="1">
+        <v>3565.66</v>
+      </c>
+      <c r="E46">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="F46">
+        <v>266.57</v>
+      </c>
+      <c r="G46">
+        <v>183.16</v>
+      </c>
+      <c r="H46">
+        <v>289.42</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47">
+        <v>13</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="1">
+        <v>5319.86</v>
+      </c>
+      <c r="E47">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="F47">
+        <v>214.29</v>
+      </c>
+      <c r="G47">
+        <v>204.25</v>
+      </c>
+      <c r="H47">
+        <v>296.29000000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48">
+        <v>14</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="1">
+        <v>4187.8900000000003</v>
+      </c>
+      <c r="E48">
+        <v>8.17</v>
+      </c>
+      <c r="F48">
+        <v>206.82</v>
+      </c>
+      <c r="G48">
+        <v>166.91</v>
+      </c>
+      <c r="H48">
+        <v>357.92</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B49">
+        <v>15</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="1">
+        <v>3615.7</v>
+      </c>
+      <c r="E49">
+        <v>8.77</v>
+      </c>
+      <c r="F49">
+        <v>160.4</v>
+      </c>
+      <c r="G49">
+        <v>97.89</v>
+      </c>
+      <c r="H49">
+        <v>547.39</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <v>16</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2807.32</v>
+      </c>
+      <c r="E50">
+        <v>9.84</v>
+      </c>
+      <c r="F50">
+        <v>152.21</v>
+      </c>
+      <c r="G50">
+        <v>141.16999999999999</v>
+      </c>
+      <c r="H50">
+        <v>292.31</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51">
+        <v>17</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" s="1">
+        <v>3761.42</v>
+      </c>
+      <c r="E51">
+        <v>7.67</v>
+      </c>
+      <c r="F51">
+        <v>148.41</v>
+      </c>
+      <c r="G51">
+        <v>83</v>
+      </c>
+      <c r="H51">
+        <v>489.54</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <v>18</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2719.29</v>
+      </c>
+      <c r="E52">
+        <v>10.81</v>
+      </c>
+      <c r="F52">
+        <v>146.46</v>
+      </c>
+      <c r="G52">
+        <v>90.33</v>
+      </c>
+      <c r="H52">
+        <v>396.8</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <v>19</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D53" s="1">
+        <v>2982.2</v>
+      </c>
+      <c r="E53">
+        <v>6.54</v>
+      </c>
+      <c r="F53">
+        <v>146.35</v>
+      </c>
+      <c r="G53">
+        <v>103.51</v>
+      </c>
+      <c r="H53">
+        <v>412.92</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <v>20</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="1">
+        <v>2185.35</v>
+      </c>
+      <c r="E54">
+        <v>8.5</v>
+      </c>
+      <c r="F54">
+        <v>119.74</v>
+      </c>
+      <c r="G54">
+        <v>85.96</v>
+      </c>
+      <c r="H54">
+        <v>136.58000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B55">
+        <v>21</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="1">
+        <v>1255.3599999999999</v>
+      </c>
+      <c r="E55">
+        <v>10.66</v>
+      </c>
+      <c r="F55">
+        <v>113.85</v>
+      </c>
+      <c r="G55">
+        <v>96.86</v>
+      </c>
+      <c r="H55">
+        <v>156.52000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B56">
+        <v>22</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" s="1">
+        <v>1560.26</v>
+      </c>
+      <c r="E56">
+        <v>8.67</v>
+      </c>
+      <c r="F56">
+        <v>109.08</v>
+      </c>
+      <c r="G56">
+        <v>59.34</v>
+      </c>
+      <c r="H56">
+        <v>370.19</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <v>23</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="1">
+        <v>2153.65</v>
+      </c>
+      <c r="E57">
+        <v>9.64</v>
+      </c>
+      <c r="F57">
+        <v>108.2</v>
+      </c>
+      <c r="G57">
+        <v>86.91</v>
+      </c>
+      <c r="H57">
+        <v>242.37</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B58">
+        <v>24</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="1">
+        <v>2657.7</v>
+      </c>
+      <c r="E58">
+        <v>9.02</v>
+      </c>
+      <c r="F58">
+        <v>107.67</v>
+      </c>
+      <c r="G58">
+        <v>81.290000000000006</v>
+      </c>
+      <c r="H58">
+        <v>195.38</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B59">
+        <v>25</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" s="1">
+        <v>2508.23</v>
+      </c>
+      <c r="E59">
+        <v>6.14</v>
+      </c>
+      <c r="F59">
+        <v>107.29</v>
+      </c>
+      <c r="G59">
+        <v>102.21</v>
+      </c>
+      <c r="H59">
+        <v>183.25</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B60">
+        <v>26</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1362.04</v>
+      </c>
+      <c r="E60">
+        <v>5.9</v>
+      </c>
+      <c r="F60">
+        <v>95.01</v>
+      </c>
+      <c r="G60">
+        <v>57.8</v>
+      </c>
+      <c r="H60">
+        <v>443.07</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B61">
+        <v>27</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="1">
+        <v>1802.98</v>
+      </c>
+      <c r="E61">
+        <v>6.57</v>
+      </c>
+      <c r="F61">
+        <v>86.27</v>
+      </c>
+      <c r="G61">
+        <v>60.51</v>
+      </c>
+      <c r="H61">
+        <v>170.96</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B62">
+        <v>28</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1348.43</v>
+      </c>
+      <c r="E62">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="F62">
+        <v>78.819999999999993</v>
+      </c>
+      <c r="G62">
+        <v>75.06</v>
+      </c>
+      <c r="H62">
+        <v>182.37</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B63">
+        <v>29</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="1">
+        <v>6004.16</v>
+      </c>
+      <c r="E63">
+        <v>8.16</v>
+      </c>
+      <c r="F63">
+        <v>77.760000000000005</v>
+      </c>
+      <c r="G63">
+        <v>61.3</v>
+      </c>
+      <c r="H63">
+        <v>160.56</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B64">
+        <v>30</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1407.2</v>
+      </c>
+      <c r="E64">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F64">
+        <v>71.52</v>
+      </c>
+      <c r="G64">
+        <v>49.64</v>
+      </c>
+      <c r="H64">
+        <v>81.67</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B65">
+        <v>31</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D65" s="1">
+        <v>2532.84</v>
+      </c>
+      <c r="E65">
+        <v>7.95</v>
+      </c>
+      <c r="F65">
+        <v>69.42</v>
+      </c>
+      <c r="G65">
+        <v>47.78</v>
+      </c>
+      <c r="H65">
+        <v>192.35</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B66">
+        <v>32</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1588.24</v>
+      </c>
+      <c r="E66">
+        <v>7.9</v>
+      </c>
+      <c r="F66">
+        <v>64.28</v>
+      </c>
+      <c r="G66">
+        <v>56.08</v>
+      </c>
+      <c r="H66">
+        <v>83.59</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B67">
+        <v>33</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D67">
+        <v>910.09</v>
+      </c>
+      <c r="E67">
+        <v>11.69</v>
+      </c>
+      <c r="F67">
+        <v>64.03</v>
+      </c>
+      <c r="G67">
+        <v>61.97</v>
+      </c>
+      <c r="H67">
+        <v>157.85</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1EDBE0-3124-40C2-B2D8-015FE455C1B1}">
+  <dimension ref="B1:H67"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1">
+        <v>127577.42</v>
+      </c>
+      <c r="E3">
+        <v>8.27</v>
+      </c>
+      <c r="F3" s="1">
+        <v>14105.04</v>
+      </c>
+      <c r="G3" s="1">
+        <v>10785.23</v>
+      </c>
+      <c r="H3" s="1">
+        <v>18247.009999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1">
+        <v>127577.42</v>
+      </c>
+      <c r="E4">
+        <v>8.27</v>
+      </c>
+      <c r="F4" s="1">
+        <v>14105.04</v>
+      </c>
+      <c r="G4" s="1">
+        <v>10785.23</v>
+      </c>
+      <c r="H4" s="1">
+        <v>18247.009999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="1">
+        <v>31473.84</v>
+      </c>
+      <c r="E5">
+        <v>7.26</v>
+      </c>
+      <c r="F5" s="1">
+        <v>4257.7</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3450.41</v>
+      </c>
+      <c r="H5" s="1">
+        <v>4570.22</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="1">
+        <v>31473.84</v>
+      </c>
+      <c r="E6">
+        <v>7.26</v>
+      </c>
+      <c r="F6" s="1">
+        <v>4257.7</v>
+      </c>
+      <c r="G6" s="1">
+        <v>3450.41</v>
+      </c>
+      <c r="H6" s="1">
+        <v>4570.22</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="1">
+        <v>28848.959999999999</v>
+      </c>
+      <c r="E7">
+        <v>8.32</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1884.26</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1410.06</v>
+      </c>
+      <c r="H7" s="1">
+        <v>3021.18</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="1">
+        <v>28848.959999999999</v>
+      </c>
+      <c r="E8">
+        <v>8.32</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1884.26</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1410.06</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3021.18</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="1">
+        <v>12349.22</v>
+      </c>
+      <c r="E9">
+        <v>8.61</v>
+      </c>
+      <c r="F9">
+        <v>808.26</v>
+      </c>
+      <c r="G9">
+        <v>545.71</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1072.01</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="1">
+        <v>12349.22</v>
+      </c>
+      <c r="E10">
+        <v>8.61</v>
+      </c>
+      <c r="F10">
+        <v>808.26</v>
+      </c>
+      <c r="G10">
+        <v>545.71</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1072.01</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="1">
+        <v>7708.74</v>
+      </c>
+      <c r="E11">
+        <v>9.56</v>
+      </c>
+      <c r="F11">
+        <v>361.02</v>
+      </c>
+      <c r="G11">
+        <v>351.5</v>
+      </c>
+      <c r="H11">
+        <v>402.42</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="1">
+        <v>7708.74</v>
+      </c>
+      <c r="E12">
+        <v>9.56</v>
+      </c>
+      <c r="F12">
+        <v>361.02</v>
+      </c>
+      <c r="G12">
+        <v>351.5</v>
+      </c>
+      <c r="H12">
+        <v>402.42</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="1">
+        <v>5259.64</v>
+      </c>
+      <c r="E13">
+        <v>10.83</v>
+      </c>
+      <c r="F13">
+        <v>455.39</v>
+      </c>
+      <c r="G13">
+        <v>335.02</v>
+      </c>
+      <c r="H13">
+        <v>663.31</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="1">
+        <v>5259.64</v>
+      </c>
+      <c r="E14">
+        <v>10.83</v>
+      </c>
+      <c r="F14">
+        <v>455.39</v>
+      </c>
+      <c r="G14">
+        <v>335.02</v>
+      </c>
+      <c r="H14">
+        <v>663.31</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3997.86</v>
+      </c>
+      <c r="E15">
+        <v>7.52</v>
+      </c>
+      <c r="F15">
+        <v>448.19</v>
+      </c>
+      <c r="G15">
+        <v>314.14</v>
+      </c>
+      <c r="H15">
+        <v>786.66</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3997.86</v>
+      </c>
+      <c r="E16">
+        <v>7.52</v>
+      </c>
+      <c r="F16">
+        <v>448.19</v>
+      </c>
+      <c r="G16">
+        <v>314.14</v>
+      </c>
+      <c r="H16">
+        <v>786.66</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="1">
+        <v>4419.0600000000004</v>
+      </c>
+      <c r="E17">
+        <v>11.25</v>
+      </c>
+      <c r="F17">
+        <v>296</v>
+      </c>
+      <c r="G17">
+        <v>290.69</v>
+      </c>
+      <c r="H17">
+        <v>452.16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="1">
+        <v>4419.0600000000004</v>
+      </c>
+      <c r="E18">
+        <v>11.25</v>
+      </c>
+      <c r="F18">
+        <v>296</v>
+      </c>
+      <c r="G18">
+        <v>290.69</v>
+      </c>
+      <c r="H18">
+        <v>452.16</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>9</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="1">
+        <v>4968.6099999999997</v>
+      </c>
+      <c r="E19">
+        <v>-5.36</v>
+      </c>
+      <c r="F19">
+        <v>292.22000000000003</v>
+      </c>
+      <c r="G19">
+        <v>259.83</v>
+      </c>
+      <c r="H19">
+        <v>380.71</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="1">
+        <v>4968.6099999999997</v>
+      </c>
+      <c r="E20">
+        <v>-5.36</v>
+      </c>
+      <c r="F20">
+        <v>292.22000000000003</v>
+      </c>
+      <c r="G20">
+        <v>259.83</v>
+      </c>
+      <c r="H20">
+        <v>380.71</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>13</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="1">
+        <v>5319.86</v>
+      </c>
+      <c r="E21">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="F21">
+        <v>214.29</v>
+      </c>
+      <c r="G21">
+        <v>204.25</v>
+      </c>
+      <c r="H21">
+        <v>296.29000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>13</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="1">
+        <v>5319.86</v>
+      </c>
+      <c r="E22">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="F22">
+        <v>214.29</v>
+      </c>
+      <c r="G22">
+        <v>204.25</v>
+      </c>
+      <c r="H22">
+        <v>296.29000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>11</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="1">
+        <v>4128.09</v>
+      </c>
+      <c r="E23">
+        <v>8.5</v>
+      </c>
+      <c r="F23">
+        <v>274.01</v>
+      </c>
+      <c r="G23">
+        <v>196.91</v>
+      </c>
+      <c r="H23">
+        <v>265.77</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>11</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="1">
+        <v>4128.09</v>
+      </c>
+      <c r="E24">
+        <v>8.5</v>
+      </c>
+      <c r="F24">
+        <v>274.01</v>
+      </c>
+      <c r="G24">
+        <v>196.91</v>
+      </c>
+      <c r="H24">
+        <v>265.77</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>12</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="1">
+        <v>3565.66</v>
+      </c>
+      <c r="E25">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="F25">
+        <v>266.57</v>
+      </c>
+      <c r="G25">
+        <v>183.16</v>
+      </c>
+      <c r="H25">
+        <v>289.42</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <v>12</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3565.66</v>
+      </c>
+      <c r="E26">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="F26">
+        <v>266.57</v>
+      </c>
+      <c r="G26">
+        <v>183.16</v>
+      </c>
+      <c r="H26">
+        <v>289.42</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>10</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3695.31</v>
+      </c>
+      <c r="E27">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="F27">
+        <v>279.87</v>
+      </c>
+      <c r="G27">
+        <v>176.89</v>
+      </c>
+      <c r="H27">
+        <v>460.25</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <v>10</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3695.31</v>
+      </c>
+      <c r="E28">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="F28">
+        <v>279.87</v>
+      </c>
+      <c r="G28">
+        <v>176.89</v>
+      </c>
+      <c r="H28">
+        <v>460.25</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <v>14</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <v>4187.8900000000003</v>
+      </c>
+      <c r="E29">
+        <v>8.17</v>
+      </c>
+      <c r="F29">
+        <v>206.82</v>
+      </c>
+      <c r="G29">
+        <v>166.91</v>
+      </c>
+      <c r="H29">
+        <v>357.92</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <v>14</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="1">
+        <v>4187.8900000000003</v>
+      </c>
+      <c r="E30">
+        <v>8.17</v>
+      </c>
+      <c r="F30">
+        <v>206.82</v>
+      </c>
+      <c r="G30">
+        <v>166.91</v>
+      </c>
+      <c r="H30">
+        <v>357.92</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <v>16</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2807.32</v>
+      </c>
+      <c r="E31">
+        <v>9.84</v>
+      </c>
+      <c r="F31">
+        <v>152.21</v>
+      </c>
+      <c r="G31">
+        <v>141.16999999999999</v>
+      </c>
+      <c r="H31">
+        <v>292.31</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <v>16</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2807.32</v>
+      </c>
+      <c r="E32">
+        <v>9.84</v>
+      </c>
+      <c r="F32">
+        <v>152.21</v>
+      </c>
+      <c r="G32">
+        <v>141.16999999999999</v>
+      </c>
+      <c r="H32">
+        <v>292.31</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <v>19</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2982.2</v>
+      </c>
+      <c r="E33">
+        <v>6.54</v>
+      </c>
+      <c r="F33">
+        <v>146.35</v>
+      </c>
+      <c r="G33">
+        <v>103.51</v>
+      </c>
+      <c r="H33">
+        <v>412.92</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <v>19</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2982.2</v>
+      </c>
+      <c r="E34">
+        <v>6.54</v>
+      </c>
+      <c r="F34">
+        <v>146.35</v>
+      </c>
+      <c r="G34">
+        <v>103.51</v>
+      </c>
+      <c r="H34">
+        <v>412.92</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <v>25</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2508.23</v>
+      </c>
+      <c r="E35">
+        <v>6.14</v>
+      </c>
+      <c r="F35">
+        <v>107.29</v>
+      </c>
+      <c r="G35">
+        <v>102.21</v>
+      </c>
+      <c r="H35">
+        <v>183.25</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <v>25</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2508.23</v>
+      </c>
+      <c r="E36">
+        <v>6.14</v>
+      </c>
+      <c r="F36">
+        <v>107.29</v>
+      </c>
+      <c r="G36">
+        <v>102.21</v>
+      </c>
+      <c r="H36">
+        <v>183.25</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37">
+        <v>15</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" s="1">
+        <v>3615.7</v>
+      </c>
+      <c r="E37">
+        <v>8.77</v>
+      </c>
+      <c r="F37">
+        <v>160.4</v>
+      </c>
+      <c r="G37">
+        <v>97.89</v>
+      </c>
+      <c r="H37">
+        <v>547.39</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <v>15</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" s="1">
+        <v>3615.7</v>
+      </c>
+      <c r="E38">
+        <v>8.77</v>
+      </c>
+      <c r="F38">
+        <v>160.4</v>
+      </c>
+      <c r="G38">
+        <v>97.89</v>
+      </c>
+      <c r="H38">
+        <v>547.39</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39">
+        <v>21</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1255.3599999999999</v>
+      </c>
+      <c r="E39">
+        <v>10.66</v>
+      </c>
+      <c r="F39">
+        <v>113.85</v>
+      </c>
+      <c r="G39">
+        <v>96.86</v>
+      </c>
+      <c r="H39">
+        <v>156.52000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40">
+        <v>21</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1255.3599999999999</v>
+      </c>
+      <c r="E40">
+        <v>10.66</v>
+      </c>
+      <c r="F40">
+        <v>113.85</v>
+      </c>
+      <c r="G40">
+        <v>96.86</v>
+      </c>
+      <c r="H40">
+        <v>156.52000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41">
+        <v>18</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="1">
+        <v>2719.29</v>
+      </c>
+      <c r="E41">
+        <v>10.81</v>
+      </c>
+      <c r="F41">
+        <v>146.46</v>
+      </c>
+      <c r="G41">
+        <v>90.33</v>
+      </c>
+      <c r="H41">
+        <v>396.8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <v>18</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="1">
+        <v>2719.29</v>
+      </c>
+      <c r="E42">
+        <v>10.81</v>
+      </c>
+      <c r="F42">
+        <v>146.46</v>
+      </c>
+      <c r="G42">
+        <v>90.33</v>
+      </c>
+      <c r="H42">
+        <v>396.8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <v>23</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="1">
+        <v>2153.65</v>
+      </c>
+      <c r="E43">
+        <v>9.64</v>
+      </c>
+      <c r="F43">
+        <v>108.2</v>
+      </c>
+      <c r="G43">
+        <v>86.91</v>
+      </c>
+      <c r="H43">
+        <v>242.37</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44">
+        <v>23</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2153.65</v>
+      </c>
+      <c r="E44">
+        <v>9.64</v>
+      </c>
+      <c r="F44">
+        <v>108.2</v>
+      </c>
+      <c r="G44">
+        <v>86.91</v>
+      </c>
+      <c r="H44">
+        <v>242.37</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B45">
+        <v>20</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2185.35</v>
+      </c>
+      <c r="E45">
+        <v>8.5</v>
+      </c>
+      <c r="F45">
+        <v>119.74</v>
+      </c>
+      <c r="G45">
+        <v>85.96</v>
+      </c>
+      <c r="H45">
+        <v>136.58000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B46">
+        <v>20</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="1">
+        <v>2185.35</v>
+      </c>
+      <c r="E46">
+        <v>8.5</v>
+      </c>
+      <c r="F46">
+        <v>119.74</v>
+      </c>
+      <c r="G46">
+        <v>85.96</v>
+      </c>
+      <c r="H46">
+        <v>136.58000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47">
+        <v>17</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3761.42</v>
+      </c>
+      <c r="E47">
+        <v>7.67</v>
+      </c>
+      <c r="F47">
+        <v>148.41</v>
+      </c>
+      <c r="G47">
+        <v>83</v>
+      </c>
+      <c r="H47">
+        <v>489.54</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48">
+        <v>17</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="1">
+        <v>3761.42</v>
+      </c>
+      <c r="E48">
+        <v>7.67</v>
+      </c>
+      <c r="F48">
+        <v>148.41</v>
+      </c>
+      <c r="G48">
+        <v>83</v>
+      </c>
+      <c r="H48">
+        <v>489.54</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B49">
+        <v>24</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="1">
+        <v>2657.7</v>
+      </c>
+      <c r="E49">
+        <v>9.02</v>
+      </c>
+      <c r="F49">
+        <v>107.67</v>
+      </c>
+      <c r="G49">
+        <v>81.290000000000006</v>
+      </c>
+      <c r="H49">
+        <v>195.38</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <v>24</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2657.7</v>
+      </c>
+      <c r="E50">
+        <v>9.02</v>
+      </c>
+      <c r="F50">
+        <v>107.67</v>
+      </c>
+      <c r="G50">
+        <v>81.290000000000006</v>
+      </c>
+      <c r="H50">
+        <v>195.38</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51">
+        <v>28</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1348.43</v>
+      </c>
+      <c r="E51">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="F51">
+        <v>78.819999999999993</v>
+      </c>
+      <c r="G51">
+        <v>75.06</v>
+      </c>
+      <c r="H51">
+        <v>182.37</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <v>28</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1348.43</v>
+      </c>
+      <c r="E52">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="F52">
+        <v>78.819999999999993</v>
+      </c>
+      <c r="G52">
+        <v>75.06</v>
+      </c>
+      <c r="H52">
+        <v>182.37</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <v>33</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53">
+        <v>910.09</v>
+      </c>
+      <c r="E53">
+        <v>11.69</v>
+      </c>
+      <c r="F53">
+        <v>64.03</v>
+      </c>
+      <c r="G53">
+        <v>61.97</v>
+      </c>
+      <c r="H53">
+        <v>157.85</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <v>29</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="1">
+        <v>6004.16</v>
+      </c>
+      <c r="E54">
+        <v>8.16</v>
+      </c>
+      <c r="F54">
+        <v>77.760000000000005</v>
+      </c>
+      <c r="G54">
+        <v>61.3</v>
+      </c>
+      <c r="H54">
+        <v>160.56</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B55">
+        <v>29</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="1">
+        <v>6004.16</v>
+      </c>
+      <c r="E55">
+        <v>8.16</v>
+      </c>
+      <c r="F55">
+        <v>77.760000000000005</v>
+      </c>
+      <c r="G55">
+        <v>61.3</v>
+      </c>
+      <c r="H55">
+        <v>160.56</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B56">
+        <v>27</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D56" s="1">
+        <v>1802.98</v>
+      </c>
+      <c r="E56">
+        <v>6.57</v>
+      </c>
+      <c r="F56">
+        <v>86.27</v>
+      </c>
+      <c r="G56">
+        <v>60.51</v>
+      </c>
+      <c r="H56">
+        <v>170.96</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <v>27</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1802.98</v>
+      </c>
+      <c r="E57">
+        <v>6.57</v>
+      </c>
+      <c r="F57">
+        <v>86.27</v>
+      </c>
+      <c r="G57">
+        <v>60.51</v>
+      </c>
+      <c r="H57">
+        <v>170.96</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B58">
+        <v>22</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1560.26</v>
+      </c>
+      <c r="E58">
+        <v>8.67</v>
+      </c>
+      <c r="F58">
+        <v>109.08</v>
+      </c>
+      <c r="G58">
+        <v>59.34</v>
+      </c>
+      <c r="H58">
+        <v>370.19</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B59">
+        <v>22</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="1">
+        <v>1560.26</v>
+      </c>
+      <c r="E59">
+        <v>8.67</v>
+      </c>
+      <c r="F59">
+        <v>109.08</v>
+      </c>
+      <c r="G59">
+        <v>59.34</v>
+      </c>
+      <c r="H59">
+        <v>370.19</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B60">
+        <v>26</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1362.04</v>
+      </c>
+      <c r="E60">
+        <v>5.9</v>
+      </c>
+      <c r="F60">
+        <v>95.01</v>
+      </c>
+      <c r="G60">
+        <v>57.8</v>
+      </c>
+      <c r="H60">
+        <v>443.07</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B61">
+        <v>26</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" s="1">
+        <v>1362.04</v>
+      </c>
+      <c r="E61">
+        <v>5.9</v>
+      </c>
+      <c r="F61">
+        <v>95.01</v>
+      </c>
+      <c r="G61">
+        <v>57.8</v>
+      </c>
+      <c r="H61">
+        <v>443.07</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B62">
+        <v>32</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1588.24</v>
+      </c>
+      <c r="E62">
+        <v>7.9</v>
+      </c>
+      <c r="F62">
+        <v>64.28</v>
+      </c>
+      <c r="G62">
+        <v>56.08</v>
+      </c>
+      <c r="H62">
+        <v>83.59</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B63">
+        <v>32</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1588.24</v>
+      </c>
+      <c r="E63">
+        <v>7.9</v>
+      </c>
+      <c r="F63">
+        <v>64.28</v>
+      </c>
+      <c r="G63">
+        <v>56.08</v>
+      </c>
+      <c r="H63">
+        <v>83.59</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B64">
+        <v>30</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1407.2</v>
+      </c>
+      <c r="E64">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F64">
+        <v>71.52</v>
+      </c>
+      <c r="G64">
+        <v>49.64</v>
+      </c>
+      <c r="H64">
+        <v>81.67</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B65">
+        <v>30</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1407.2</v>
+      </c>
+      <c r="E65">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F65">
+        <v>71.52</v>
+      </c>
+      <c r="G65">
+        <v>49.64</v>
+      </c>
+      <c r="H65">
+        <v>81.67</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B66">
+        <v>31</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" s="1">
+        <v>2532.84</v>
+      </c>
+      <c r="E66">
+        <v>7.95</v>
+      </c>
+      <c r="F66">
+        <v>69.42</v>
+      </c>
+      <c r="G66">
+        <v>47.78</v>
+      </c>
+      <c r="H66">
+        <v>192.35</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B67">
+        <v>31</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" s="1">
+        <v>2532.84</v>
+      </c>
+      <c r="E67">
+        <v>7.95</v>
+      </c>
+      <c r="F67">
+        <v>69.42</v>
+      </c>
+      <c r="G67">
+        <v>47.78</v>
+      </c>
+      <c r="H67">
+        <v>192.35</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:H67">
+    <sortCondition descending="1" ref="G3:G67"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>